--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -657,19 +657,19 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C3" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -731,13 +731,13 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -769,13 +769,13 @@
         <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -789,11 +789,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX5"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -830,7 +830,7 @@
     <col width="26" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="18" customWidth="1" min="38" max="38"/>
-    <col width="23" customWidth="1" min="39" max="39"/>
+    <col width="20" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
@@ -1163,10 +1163,8 @@
           <t>Chandramani Chaudhary</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>9768922502</t>
-        </is>
+      <c r="O2" s="2" t="n">
+        <v>9768922502</v>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
@@ -1205,10 +1203,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -1246,19 +1242,17 @@
           <t>Fiber wire breakage suspect</t>
         </is>
       </c>
-      <c r="AH2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH2" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="AI2" s="2" t="inlineStr">
         <is>
-          <t>00:00 hour</t>
+          <t>00:52 hour</t>
         </is>
       </c>
       <c r="AJ2" s="2" t="inlineStr">
         <is>
-          <t>00:00 hour / 00:00 hour</t>
+          <t>23:08 hour / 00:00 hour</t>
         </is>
       </c>
       <c r="AK2" s="2" t="inlineStr"/>
@@ -1272,25 +1266,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN2" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN2" s="2" t="n">
+        <v>6</v>
       </c>
       <c r="AO2" s="2" t="inlineStr">
         <is>
           <t>CDB314</t>
         </is>
       </c>
-      <c r="AP2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr">
         <is>
-          <t>Case : fiber issue   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="2" t="inlineStr">
@@ -1378,7 +1368,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -1391,10 +1381,8 @@
           <t>Sudharna Byanjankar</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>9851316119</t>
-        </is>
+      <c r="O3" s="2" t="n">
+        <v>9851316119</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
@@ -1421,7 +1409,7 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>15 Sep 2026 09:04:22 AM</t>
+          <t>15 Sep 2026 10:39:23 AM</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
@@ -1429,10 +1417,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y3" s="2" t="inlineStr">
-        <is>
-          <t>27.67154</t>
-        </is>
+      <c r="Y3" s="2" t="n">
+        <v>27.67154</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1441,7 +1427,7 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>Layer 1-User</t>
+          <t>Layer 1-</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
@@ -1485,43 +1471,39 @@
       </c>
       <c r="AM3" s="2" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AN3" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t>Rahul Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN3" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="AO3" s="2" t="inlineStr">
         <is>
           <t>2,6</t>
         </is>
       </c>
-      <c r="AP3" s="2" t="inlineStr">
-        <is>
-          <t>85.33876</t>
-        </is>
+      <c r="AP3" s="2" t="n">
+        <v>85.33875999999999</v>
       </c>
       <c r="AQ3" s="2" t="inlineStr"/>
       <c r="AR3" s="2" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS3" s="2" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1h 35m</t>
         </is>
       </c>
       <c r="AT3" s="2" t="inlineStr">
         <is>
-          <t>11h 11m</t>
+          <t>12h 46m</t>
         </is>
       </c>
       <c r="AU3" s="2" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="AV3" s="2" t="inlineStr">
@@ -1548,7 +1530,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>15 Sep 2026 9:24 AM</t>
+          <t>15 Sep 2026 10:55 AM</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -1574,7 +1556,7 @@
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1584,32 +1566,32 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>TKT1334065</t>
+          <t>TKT1333510</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Saradha Panta</t>
+          <t>Kabiraj Limbu</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Saradha Panta</t>
+          <t>Kabiraj Limbu</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9851322004</t>
+          <t>9825986033</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1620,24 +1602,24 @@
       <c r="Q4" s="2" t="inlineStr"/>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>15 Sep 2026 07:57:11 AM</t>
+          <t>15 Sep 2026 10:55:56 AM</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr"/>
       <c r="T4" s="2" t="inlineStr"/>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9851322004</t>
+          <t>BKT9825986033</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15 Sep 2026 07:57:11 AM</t>
+          <t>14 Sep 2026 01:24:32 PM</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15 Sep 2026 09:38:08 AM</t>
+          <t>15 Sep 2026 10:55:56 AM</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
@@ -1645,11 +1627,7 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y4" s="2" t="inlineStr">
-        <is>
-          <t>27.71579</t>
-        </is>
-      </c>
+      <c r="Y4" s="2" t="inlineStr"/>
       <c r="Z4" s="2" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
@@ -1662,7 +1640,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>Laxman Koirala</t>
+          <t>L1  Support</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1673,12 +1651,12 @@
       <c r="AD4" s="2" t="inlineStr"/>
       <c r="AE4" s="2" t="inlineStr">
         <is>
-          <t>Sarveshwor Mahadev Temple, Nayabasti, Bagmati, Central, Nepal</t>
+          <t>Kageshwori Manohara Municipality Ward No.7 office - Local government office P92M+XX3 Kageshwori Mano</t>
         </is>
       </c>
       <c r="AF4" s="2" t="inlineStr">
         <is>
-          <t>workcgnet@gmail.com</t>
+          <t>test@test.com</t>
         </is>
       </c>
       <c r="AG4" s="2" t="inlineStr">
@@ -1687,17 +1665,21 @@
         </is>
       </c>
       <c r="AH4" s="2" t="inlineStr"/>
-      <c r="AI4" s="2" t="inlineStr"/>
+      <c r="AI4" s="2" t="inlineStr">
+        <is>
+          <t>07:31 hour</t>
+        </is>
+      </c>
       <c r="AJ4" s="2" t="inlineStr"/>
       <c r="AK4" s="2" t="inlineStr"/>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>Nisha Joshi</t>
+          <t>Kusum Gurung</t>
         </is>
       </c>
       <c r="AM4" s="2" t="inlineStr">
         <is>
-          <t>Monali Lohani</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="AN4" s="2" t="inlineStr">
@@ -1707,38 +1689,34 @@
       </c>
       <c r="AO4" s="2" t="inlineStr">
         <is>
-          <t>L31-6</t>
-        </is>
-      </c>
-      <c r="AP4" s="2" t="inlineStr">
-        <is>
-          <t>85.36397</t>
-        </is>
-      </c>
+          <t>L37-1</t>
+        </is>
+      </c>
+      <c r="AP4" s="2" t="inlineStr"/>
       <c r="AQ4" s="2" t="inlineStr"/>
       <c r="AR4" s="2" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="AS4" s="2" t="inlineStr">
         <is>
-          <t>1h 40m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="AT4" s="2" t="inlineStr">
         <is>
-          <t>1h 40m</t>
+          <t>21h 31m</t>
         </is>
       </c>
       <c r="AU4" s="2" t="inlineStr">
         <is>
-          <t>Other / In Progress (In Progress)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="AV4" s="2" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="AW4" s="2" t="inlineStr">
@@ -1760,7 +1738,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>15 Sep 2026 8:51 AM</t>
+          <t>15 Sep 2026 9:24 AM</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1786,7 +1764,7 @@
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1796,17 +1774,17 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>TKT1333787</t>
+          <t>TKT1334065</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Ganesh bahadur dhakal</t>
+          <t>Saradha Panta</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -1816,12 +1794,12 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Ganesh bahadur dhakal</t>
+          <t>Saradha Panta</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9841051986</t>
+          <t>9851322004</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1832,24 +1810,24 @@
       <c r="Q5" s="2" t="inlineStr"/>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>15 Sep 2026 08:51:57 AM</t>
+          <t>15 Sep 2026 07:57:11 AM</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr"/>
       <c r="T5" s="2" t="inlineStr"/>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>9841051986</t>
+          <t>9851322004</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14 Sep 2026 05:06:15 PM</t>
+          <t>15 Sep 2026 07:57:11 AM</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15 Sep 2026 08:51:57 AM</t>
+          <t>15 Sep 2026 09:38:08 AM</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
@@ -1857,7 +1835,11 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y5" s="2" t="inlineStr"/>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>27.71579</t>
+        </is>
+      </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
@@ -1870,7 +1852,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>L1  Support</t>
+          <t>Laxman Koirala</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1881,31 +1863,31 @@
       <c r="AD5" s="2" t="inlineStr"/>
       <c r="AE5" s="2" t="inlineStr">
         <is>
-          <t>Dhakchin dhoka the luga ghar, Bagmati, Central, Nepal</t>
-        </is>
-      </c>
-      <c r="AF5" s="2" t="inlineStr"/>
+          <t>Sarveshwor Mahadev Temple, Nayabasti, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="2" t="inlineStr">
+        <is>
+          <t>workcgnet@gmail.com</t>
+        </is>
+      </c>
       <c r="AG5" s="2" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="AH5" s="2" t="inlineStr"/>
-      <c r="AI5" s="2" t="inlineStr">
-        <is>
-          <t>02:54 hour</t>
-        </is>
-      </c>
+      <c r="AI5" s="2" t="inlineStr"/>
       <c r="AJ5" s="2" t="inlineStr"/>
       <c r="AK5" s="2" t="inlineStr"/>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>Aakash Shah</t>
+          <t>Nisha Joshi</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>Sabin Giri</t>
+          <t>Monali Lohani</t>
         </is>
       </c>
       <c r="AN5" s="2" t="inlineStr">
@@ -1915,42 +1897,250 @@
       </c>
       <c r="AO5" s="2" t="inlineStr">
         <is>
-          <t>L15-2</t>
-        </is>
-      </c>
-      <c r="AP5" s="2" t="inlineStr"/>
+          <t>L31-6</t>
+        </is>
+      </c>
+      <c r="AP5" s="2" t="inlineStr">
+        <is>
+          <t>85.36397</t>
+        </is>
+      </c>
       <c r="AQ5" s="2" t="inlineStr"/>
       <c r="AR5" s="2" t="inlineStr">
         <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS5" s="2" t="inlineStr">
+        <is>
+          <t>1h 40m</t>
+        </is>
+      </c>
+      <c r="AT5" s="2" t="inlineStr">
+        <is>
+          <t>1h 40m</t>
+        </is>
+      </c>
+      <c r="AU5" s="2" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV5" s="2" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW5" s="2" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX5" s="2" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 8:51 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>Case : wifi 6   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS5" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>TKT1333787</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Ganesh bahadur dhakal</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Ganesh bahadur dhakal</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>9841051986</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 08:51:57 AM</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>9841051986</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 05:06:15 PM</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 08:51:57 AM</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="inlineStr">
+        <is>
+          <t>Dhakchin dhoka the luga ghar, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AG6" s="2" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH6" s="2" t="inlineStr"/>
+      <c r="AI6" s="2" t="inlineStr">
+        <is>
+          <t>02:54 hour</t>
+        </is>
+      </c>
+      <c r="AJ6" s="2" t="inlineStr"/>
+      <c r="AK6" s="2" t="inlineStr"/>
+      <c r="AL6" s="2" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM6" s="2" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN6" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO6" s="2" t="inlineStr">
+        <is>
+          <t>L15-2</t>
+        </is>
+      </c>
+      <c r="AP6" s="2" t="inlineStr"/>
+      <c r="AQ6" s="2" t="inlineStr"/>
+      <c r="AR6" s="2" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS6" s="2" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT5" s="2" t="inlineStr">
+      <c r="AT6" s="2" t="inlineStr">
         <is>
           <t>15h 45m</t>
         </is>
       </c>
-      <c r="AU5" s="2" t="inlineStr">
+      <c r="AU6" s="2" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV5" s="2" t="inlineStr">
+      <c r="AV6" s="2" t="inlineStr">
         <is>
           <t>Case : wifi 6   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AW5" s="2" t="inlineStr">
+      <c r="AW6" s="2" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX5" s="2" t="inlineStr">
+      <c r="AX6" s="2" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Sep_2026.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -510,11 +510,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Chandramani Tharu</t>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>0</v>
@@ -528,52 +528,142 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Sabin Giri</t>
+          <t>Chandramani Tharu</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Om Neupane</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>👥 GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B10" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C10" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>60.0%</t>
         </is>
@@ -684,14 +774,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -702,20 +797,45 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Om Neupane</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -731,12 +851,27 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="G2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="I2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="4" t="n">
         <v>4</v>
       </c>
     </row>
@@ -747,15 +882,30 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="D3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -766,15 +916,30 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="I4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -789,7 +954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX6"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -842,6 +1007,7 @@
     <col width="45" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
     <col width="23" customWidth="1" min="50" max="50"/>
+    <col width="16" customWidth="1" min="51" max="51"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1095,6 +1261,11 @@
           <t>Employee Name</t>
         </is>
       </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>Is_Solved_Val</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1278,11 +1449,7 @@
         <v>0</v>
       </c>
       <c r="AQ2" s="2" t="inlineStr"/>
-      <c r="AR2" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="AR2" s="2" t="inlineStr"/>
       <c r="AS2" s="2" t="inlineStr">
         <is>
           <t>7m</t>
@@ -1312,6 +1479,9 @@
         <is>
           <t>Chandramani Tharu</t>
         </is>
+      </c>
+      <c r="AY2" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1486,11 +1656,7 @@
         <v>85.33875999999999</v>
       </c>
       <c r="AQ3" s="2" t="inlineStr"/>
-      <c r="AR3" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="AR3" s="2" t="inlineStr"/>
       <c r="AS3" s="2" t="inlineStr">
         <is>
           <t>1h 35m</t>
@@ -1520,6 +1686,9 @@
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
+      </c>
+      <c r="AY3" s="2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1579,20 +1748,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>Kabiraj Limbu</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>9825986033</t>
-        </is>
+      <c r="O4" s="2" t="n">
+        <v>9825986033</v>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
@@ -1682,10 +1845,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN4" s="2" t="n">
+        <v>6</v>
       </c>
       <c r="AO4" s="2" t="inlineStr">
         <is>
@@ -1729,6 +1890,9 @@
           <t>Sabin Giri</t>
         </is>
       </c>
+      <c r="AY4" s="2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1797,10 +1961,8 @@
           <t>Saradha Panta</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>9851322004</t>
-        </is>
+      <c r="O5" s="2" t="n">
+        <v>9851322004</v>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
@@ -1835,10 +1997,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y5" s="2" t="inlineStr">
-        <is>
-          <t>27.71579</t>
-        </is>
+      <c r="Y5" s="2" t="n">
+        <v>27.71579</v>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
@@ -1890,20 +2050,16 @@
           <t>Monali Lohani</t>
         </is>
       </c>
-      <c r="AN5" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN5" s="2" t="n">
+        <v>6</v>
       </c>
       <c r="AO5" s="2" t="inlineStr">
         <is>
           <t>L31-6</t>
         </is>
       </c>
-      <c r="AP5" s="2" t="inlineStr">
-        <is>
-          <t>85.36397</t>
-        </is>
+      <c r="AP5" s="2" t="n">
+        <v>85.36396999999999</v>
       </c>
       <c r="AQ5" s="2" t="inlineStr"/>
       <c r="AR5" s="2" t="inlineStr">
@@ -1940,6 +2096,9 @@
         <is>
           <t>Sabin Giri</t>
         </is>
+      </c>
+      <c r="AY5" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -2009,10 +2168,8 @@
           <t>Ganesh bahadur dhakal</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>9841051986</t>
-        </is>
+      <c r="O6" s="2" t="n">
+        <v>9841051986</v>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
@@ -2098,10 +2255,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN6" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN6" s="2" t="n">
+        <v>6</v>
       </c>
       <c r="AO6" s="2" t="inlineStr">
         <is>
@@ -2144,6 +2299,9 @@
         <is>
           <t>Sabin Giri</t>
         </is>
+      </c>
+      <c r="AY6" s="2" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Sep_2026.xlsx
@@ -20,13 +20,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <name val="Segoe UI"/>
@@ -77,13 +80,19 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
     <border>
       <left style="thin">
@@ -103,14 +112,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -486,186 +504,186 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Employee Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="B3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Om Neupane</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="B7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+      <c r="B8" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>👥 GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>60.0%</t>
+      <c r="B10" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>63.6%</t>
         </is>
       </c>
     </row>
@@ -680,7 +698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -691,75 +709,98 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Task / Issue Type</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Total_Tickets</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Solved_Count</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>% Share of Total</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>20.0%</t>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>9.1%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>9.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>80.0%</t>
+      <c r="B4" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>87.5%</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -774,7 +815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -790,157 +831,225 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Om Neupane</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2" t="n">
+      <c r="B2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="2" t="n">
+      <c r="G2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="4" t="n">
-        <v>4</v>
+      <c r="H2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="6" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Fiber wire breakage suspect</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="2" t="n">
+      <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="4" t="n">
+      <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Other / Uncategorized</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Replace SKYCOM to NETTV</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="3" t="n">
+      <c r="B6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>5</v>
+      <c r="D6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -954,7 +1063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AX12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -965,7 +1074,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
@@ -995,7 +1104,7 @@
     <col width="26" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="18" customWidth="1" min="38" max="38"/>
-    <col width="20" customWidth="1" min="39" max="39"/>
+    <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
@@ -1007,1301 +1116,2444 @@
     <col width="45" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
     <col width="23" customWidth="1" min="50" max="50"/>
-    <col width="16" customWidth="1" min="51" max="51"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Target Employee</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Grid Date</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Grid User Name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Grid Employee Name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Grid Module</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Grid Operation</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Grid IP Address</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Grid Remark</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Case Origin</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>Customer Name</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Mobile No</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Sub Sub Category</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>Estimated closed time based on SLA</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>Estimated closed time based on TAT</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>User Id</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" s="2" t="inlineStr">
         <is>
           <t>Associated Location Status</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" s="2" t="inlineStr">
         <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" s="2" t="inlineStr">
         <is>
           <t>Case Reason</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" s="2" t="inlineStr">
         <is>
           <t>Assign Team</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" s="2" t="inlineStr">
         <is>
           <t>Assign User</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" s="2" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" s="2" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" s="2" t="inlineStr">
         <is>
           <t>Customer Address</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" s="2" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" s="2" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" s="2" t="inlineStr">
         <is>
           <t>Escalated Layer</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" s="2" t="inlineStr">
         <is>
           <t>SLA</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" s="2" t="inlineStr">
         <is>
           <t>SLA Left/Total</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" s="2" t="inlineStr">
         <is>
           <t>TAT Left/Total</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" s="2" t="inlineStr">
         <is>
           <t>Created By</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" s="2" t="inlineStr">
         <is>
           <t>Last Modified By</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" s="2" t="inlineStr">
         <is>
           <t>Associated Location Level</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" s="2" t="inlineStr">
         <is>
           <t>Associated Location Name</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" s="2" t="inlineStr">
         <is>
           <t>Longitude</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" s="2" t="inlineStr">
         <is>
           <t>Solution Given</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" s="2" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" s="2" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" s="2" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" s="2" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" s="2" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" s="2" t="inlineStr">
         <is>
           <t>Task / Issue Type</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" s="2" t="inlineStr">
         <is>
           <t>Employee Name</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>Is_Solved_Val</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 9:35 AM</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Case</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Update</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Case : fiber issue   has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>fiber issue</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>TKT1334123</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>Chandramani Chaudhary</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>Chandramani Chaudhary</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="O2" s="3" t="n">
         <v>9768922502</v>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>No Internet Connection</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr"/>
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 09:27:54 AM</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="S2" s="3" t="inlineStr">
         <is>
           <t>17 Sep 2026 01: 26:00 PM</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr"/>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="T2" s="3" t="inlineStr"/>
+      <c r="U2" s="3" t="inlineStr">
         <is>
           <t>LTP9768922502</t>
         </is>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="V2" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 09:26:46 AM</t>
         </is>
       </c>
-      <c r="W2" s="2" t="inlineStr">
+      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 09:35:50 AM</t>
         </is>
       </c>
-      <c r="X2" s="2" t="inlineStr">
+      <c r="X2" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="Y2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" s="2" t="inlineStr">
+      <c r="Y2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="3" t="inlineStr">
         <is>
           <t>No Internet Connection</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
+      <c r="AA2" s="3" t="inlineStr">
         <is>
           <t>Layer 2-CG Group</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
+      <c r="AB2" s="3" t="inlineStr">
         <is>
           <t>Hari Rijal</t>
         </is>
       </c>
-      <c r="AC2" s="2" t="inlineStr">
+      <c r="AC2" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AD2" s="2" t="inlineStr"/>
-      <c r="AE2" s="2" t="inlineStr">
+      <c r="AD2" s="3" t="inlineStr"/>
+      <c r="AE2" s="3" t="inlineStr">
         <is>
           <t>Hyundai Service Kupondole - Hyundai dealer Kupondole Hts Rd Lalitpur 44600, Lalitpur, Nepal, Nepal</t>
         </is>
       </c>
-      <c r="AF2" s="2" t="inlineStr">
+      <c r="AF2" s="3" t="inlineStr">
         <is>
           <t>chandramanitharu@gmail.com</t>
         </is>
       </c>
-      <c r="AG2" s="2" t="inlineStr">
+      <c r="AG2" s="3" t="inlineStr">
         <is>
           <t>Fiber wire breakage suspect</t>
         </is>
       </c>
-      <c r="AH2" s="2" t="n">
+      <c r="AH2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="AI2" s="2" t="inlineStr">
+      <c r="AI2" s="3" t="inlineStr">
         <is>
           <t>00:52 hour</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="inlineStr">
+      <c r="AJ2" s="3" t="inlineStr">
         <is>
           <t>23:08 hour / 00:00 hour</t>
         </is>
       </c>
-      <c r="AK2" s="2" t="inlineStr"/>
-      <c r="AL2" s="2" t="inlineStr">
+      <c r="AK2" s="3" t="inlineStr"/>
+      <c r="AL2" s="3" t="inlineStr">
         <is>
           <t>Manisha kunwar</t>
         </is>
       </c>
-      <c r="AM2" s="2" t="inlineStr">
+      <c r="AM2" s="3" t="inlineStr">
         <is>
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN2" s="2" t="n">
+      <c r="AN2" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AO2" s="2" t="inlineStr">
+      <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>CDB314</t>
         </is>
       </c>
-      <c r="AP2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" s="2" t="inlineStr"/>
-      <c r="AR2" s="2" t="inlineStr"/>
-      <c r="AS2" s="2" t="inlineStr">
+      <c r="AP2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" s="3" t="inlineStr"/>
+      <c r="AR2" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS2" s="3" t="inlineStr">
         <is>
           <t>7m</t>
         </is>
       </c>
-      <c r="AT2" s="2" t="inlineStr">
+      <c r="AT2" s="3" t="inlineStr">
         <is>
           <t>9m</t>
         </is>
       </c>
-      <c r="AU2" s="2" t="inlineStr">
+      <c r="AU2" s="3" t="inlineStr">
         <is>
           <t>Other / In Progress (In Progress)</t>
         </is>
       </c>
-      <c r="AV2" s="2" t="inlineStr">
+      <c r="AV2" s="3" t="inlineStr">
         <is>
           <t>Case : fiber issue   has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AW2" s="2" t="inlineStr">
+      <c r="AW2" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AX2" s="2" t="inlineStr">
+      <c r="AX2" s="3" t="inlineStr">
         <is>
           <t>Chandramani Tharu</t>
         </is>
-      </c>
-      <c r="AY2" s="2" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 9:04 AM</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Case</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Update</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>WiFi 6</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>TKT1333983</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>Sudharna Byanjankar</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>Sudharna Byanjankar</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="O3" s="3" t="n">
         <v>9851316119</v>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 09:04:22 AM</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr"/>
-      <c r="T3" s="2" t="inlineStr"/>
-      <c r="U3" s="2" t="inlineStr">
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
         <is>
           <t>9849181580</t>
         </is>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="V3" s="3" t="inlineStr">
         <is>
           <t>14 Sep 2026 09:52:27 PM</t>
         </is>
       </c>
-      <c r="W3" s="2" t="inlineStr">
+      <c r="W3" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 10:39:23 AM</t>
         </is>
       </c>
-      <c r="X3" s="2" t="inlineStr">
+      <c r="X3" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="Y3" s="2" t="n">
+      <c r="Y3" s="3" t="n">
         <v>27.67154</v>
       </c>
-      <c r="Z3" s="2" t="inlineStr">
+      <c r="Z3" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
+      <c r="AA3" s="3" t="inlineStr">
         <is>
           <t>Layer 1-</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
+      <c r="AB3" s="3" t="inlineStr">
         <is>
           <t>L1  Support</t>
         </is>
       </c>
-      <c r="AC3" s="2" t="inlineStr">
+      <c r="AC3" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AD3" s="2" t="inlineStr"/>
-      <c r="AE3" s="2" t="inlineStr">
+      <c r="AD3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr">
         <is>
           <t>Balkumari, Indira Pharmacy nearby, 8, Bagmati, Central, Nepal</t>
         </is>
       </c>
-      <c r="AF3" s="2" t="inlineStr">
+      <c r="AF3" s="3" t="inlineStr">
         <is>
           <t>byanjankar.sudharna@gmail.com</t>
         </is>
       </c>
-      <c r="AG3" s="2" t="inlineStr">
+      <c r="AG3" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH3" s="2" t="inlineStr"/>
-      <c r="AI3" s="2" t="inlineStr">
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr">
         <is>
           <t>00:00 hour</t>
         </is>
       </c>
-      <c r="AJ3" s="2" t="inlineStr"/>
-      <c r="AK3" s="2" t="inlineStr"/>
-      <c r="AL3" s="2" t="inlineStr">
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr">
         <is>
           <t>Nirajan Dhamala</t>
         </is>
       </c>
-      <c r="AM3" s="2" t="inlineStr">
+      <c r="AM3" s="3" t="inlineStr">
         <is>
           <t>Rahul Chaudhary</t>
         </is>
       </c>
-      <c r="AN3" s="2" t="n">
+      <c r="AN3" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="AO3" s="2" t="inlineStr">
+      <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>2,6</t>
         </is>
       </c>
-      <c r="AP3" s="2" t="n">
+      <c r="AP3" s="3" t="n">
         <v>85.33875999999999</v>
       </c>
-      <c r="AQ3" s="2" t="inlineStr"/>
-      <c r="AR3" s="2" t="inlineStr"/>
-      <c r="AS3" s="2" t="inlineStr">
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
         <is>
           <t>1h 35m</t>
         </is>
       </c>
-      <c r="AT3" s="2" t="inlineStr">
+      <c r="AT3" s="3" t="inlineStr">
         <is>
           <t>12h 46m</t>
         </is>
       </c>
-      <c r="AU3" s="2" t="inlineStr">
+      <c r="AU3" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="AV3" s="2" t="inlineStr">
+      <c r="AV3" s="3" t="inlineStr">
         <is>
           <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AW3" s="2" t="inlineStr">
+      <c r="AW3" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX3" s="2" t="inlineStr">
+      <c r="AX3" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
-      </c>
-      <c r="AY3" s="2" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 10:55 AM</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Case</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Update</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>wifi 6</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>TKT1333510</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Kabiraj Limbu</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr"/>
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Kabiraj Limbu</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
+      <c r="O4" s="3" t="n">
         <v>9825986033</v>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 10:55:56 AM</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr"/>
-      <c r="T4" s="2" t="inlineStr"/>
-      <c r="U4" s="2" t="inlineStr">
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
         <is>
           <t>BKT9825986033</t>
         </is>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V4" s="3" t="inlineStr">
         <is>
           <t>14 Sep 2026 01:24:32 PM</t>
         </is>
       </c>
-      <c r="W4" s="2" t="inlineStr">
+      <c r="W4" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 10:55:56 AM</t>
         </is>
       </c>
-      <c r="X4" s="2" t="inlineStr">
+      <c r="X4" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="Y4" s="2" t="inlineStr"/>
-      <c r="Z4" s="2" t="inlineStr">
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
+      <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>Layer 1-User</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
+      <c r="AB4" s="3" t="inlineStr">
         <is>
           <t>L1  Support</t>
         </is>
       </c>
-      <c r="AC4" s="2" t="inlineStr">
+      <c r="AC4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="inlineStr">
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
         <is>
           <t>Kageshwori Manohara Municipality Ward No.7 office - Local government office P92M+XX3 Kageshwori Mano</t>
         </is>
       </c>
-      <c r="AF4" s="2" t="inlineStr">
+      <c r="AF4" s="3" t="inlineStr">
         <is>
           <t>test@test.com</t>
         </is>
       </c>
-      <c r="AG4" s="2" t="inlineStr">
+      <c r="AG4" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH4" s="2" t="inlineStr"/>
-      <c r="AI4" s="2" t="inlineStr">
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr">
         <is>
           <t>07:31 hour</t>
         </is>
       </c>
-      <c r="AJ4" s="2" t="inlineStr"/>
-      <c r="AK4" s="2" t="inlineStr"/>
-      <c r="AL4" s="2" t="inlineStr">
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
         <is>
           <t>Kusum Gurung</t>
         </is>
       </c>
-      <c r="AM4" s="2" t="inlineStr">
+      <c r="AM4" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN4" s="2" t="n">
+      <c r="AN4" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AO4" s="2" t="inlineStr">
+      <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>L37-1</t>
         </is>
       </c>
-      <c r="AP4" s="2" t="inlineStr"/>
-      <c r="AQ4" s="2" t="inlineStr"/>
-      <c r="AR4" s="2" t="inlineStr">
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>21h 31m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS4" s="2" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT4" s="2" t="inlineStr">
-        <is>
-          <t>21h 31m</t>
-        </is>
-      </c>
-      <c r="AU4" s="2" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV4" s="2" t="inlineStr">
-        <is>
-          <t>Case : wifi 6   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW4" s="2" t="inlineStr">
+      <c r="AW4" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX4" s="2" t="inlineStr">
+      <c r="AX4" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
         </is>
-      </c>
-      <c r="AY4" s="2" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 9:24 AM</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Case</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Update</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>wifi 6</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>TKT1334065</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>Saradha Panta</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>Saradha Panta</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="O5" s="3" t="n">
         <v>9851322004</v>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr">
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 07:57:11 AM</t>
         </is>
       </c>
-      <c r="S5" s="2" t="inlineStr"/>
-      <c r="T5" s="2" t="inlineStr"/>
-      <c r="U5" s="2" t="inlineStr">
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
         <is>
           <t>9851322004</t>
         </is>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V5" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 07:57:11 AM</t>
         </is>
       </c>
-      <c r="W5" s="2" t="inlineStr">
+      <c r="W5" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 09:38:08 AM</t>
         </is>
       </c>
-      <c r="X5" s="2" t="inlineStr">
+      <c r="X5" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="Y5" s="2" t="n">
+      <c r="Y5" s="3" t="n">
         <v>27.71579</v>
       </c>
-      <c r="Z5" s="2" t="inlineStr">
+      <c r="Z5" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
+      <c r="AA5" s="3" t="inlineStr">
         <is>
           <t>Layer 1-User</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
+      <c r="AB5" s="3" t="inlineStr">
         <is>
           <t>Laxman Koirala</t>
         </is>
       </c>
-      <c r="AC5" s="2" t="inlineStr">
+      <c r="AC5" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AD5" s="2" t="inlineStr"/>
-      <c r="AE5" s="2" t="inlineStr">
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
         <is>
           <t>Sarveshwor Mahadev Temple, Nayabasti, Bagmati, Central, Nepal</t>
         </is>
       </c>
-      <c r="AF5" s="2" t="inlineStr">
+      <c r="AF5" s="3" t="inlineStr">
         <is>
           <t>workcgnet@gmail.com</t>
         </is>
       </c>
-      <c r="AG5" s="2" t="inlineStr">
+      <c r="AG5" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH5" s="2" t="inlineStr"/>
-      <c r="AI5" s="2" t="inlineStr"/>
-      <c r="AJ5" s="2" t="inlineStr"/>
-      <c r="AK5" s="2" t="inlineStr"/>
-      <c r="AL5" s="2" t="inlineStr">
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr"/>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
         <is>
           <t>Nisha Joshi</t>
         </is>
       </c>
-      <c r="AM5" s="2" t="inlineStr">
+      <c r="AM5" s="3" t="inlineStr">
         <is>
           <t>Monali Lohani</t>
         </is>
       </c>
-      <c r="AN5" s="2" t="n">
+      <c r="AN5" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AO5" s="2" t="inlineStr">
+      <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>L31-6</t>
         </is>
       </c>
-      <c r="AP5" s="2" t="n">
+      <c r="AP5" s="3" t="n">
         <v>85.36396999999999</v>
       </c>
-      <c r="AQ5" s="2" t="inlineStr"/>
-      <c r="AR5" s="2" t="inlineStr">
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>1h 40m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>1h 40m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS5" s="2" t="inlineStr">
-        <is>
-          <t>1h 40m</t>
-        </is>
-      </c>
-      <c r="AT5" s="2" t="inlineStr">
-        <is>
-          <t>1h 40m</t>
-        </is>
-      </c>
-      <c r="AU5" s="2" t="inlineStr">
-        <is>
-          <t>Other / In Progress (In Progress)</t>
-        </is>
-      </c>
-      <c r="AV5" s="2" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW5" s="2" t="inlineStr">
+      <c r="AW5" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX5" s="2" t="inlineStr">
+      <c r="AX5" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
         </is>
-      </c>
-      <c r="AY5" s="2" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 8:51 AM</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>Case</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Update</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>wifi 6</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>TKT1333787</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>Ganesh bahadur dhakal</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>Ganesh bahadur dhakal</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="O6" s="3" t="n">
         <v>9841051986</v>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P6" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr">
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 08:51:57 AM</t>
         </is>
       </c>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr"/>
-      <c r="U6" s="2" t="inlineStr">
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
         <is>
           <t>9841051986</t>
         </is>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V6" s="3" t="inlineStr">
         <is>
           <t>14 Sep 2026 05:06:15 PM</t>
         </is>
       </c>
-      <c r="W6" s="2" t="inlineStr">
+      <c r="W6" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 08:51:57 AM</t>
         </is>
       </c>
-      <c r="X6" s="2" t="inlineStr">
+      <c r="X6" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="Y6" s="2" t="inlineStr"/>
-      <c r="Z6" s="2" t="inlineStr">
+      <c r="Y6" s="3" t="inlineStr"/>
+      <c r="Z6" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
+      <c r="AA6" s="3" t="inlineStr">
         <is>
           <t>Layer 1-User</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
+      <c r="AB6" s="3" t="inlineStr">
         <is>
           <t>L1  Support</t>
         </is>
       </c>
-      <c r="AC6" s="2" t="inlineStr">
+      <c r="AC6" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AD6" s="2" t="inlineStr"/>
-      <c r="AE6" s="2" t="inlineStr">
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
         <is>
           <t>Dhakchin dhoka the luga ghar, Bagmati, Central, Nepal</t>
         </is>
       </c>
-      <c r="AF6" s="2" t="inlineStr"/>
-      <c r="AG6" s="2" t="inlineStr">
+      <c r="AF6" s="3" t="inlineStr"/>
+      <c r="AG6" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH6" s="2" t="inlineStr"/>
-      <c r="AI6" s="2" t="inlineStr">
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr">
         <is>
           <t>02:54 hour</t>
         </is>
       </c>
-      <c r="AJ6" s="2" t="inlineStr"/>
-      <c r="AK6" s="2" t="inlineStr"/>
-      <c r="AL6" s="2" t="inlineStr">
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
         <is>
           <t>Aakash Shah</t>
         </is>
       </c>
-      <c r="AM6" s="2" t="inlineStr">
+      <c r="AM6" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN6" s="2" t="n">
+      <c r="AN6" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AO6" s="2" t="inlineStr">
+      <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>L15-2</t>
         </is>
       </c>
-      <c r="AP6" s="2" t="inlineStr"/>
-      <c r="AQ6" s="2" t="inlineStr"/>
-      <c r="AR6" s="2" t="inlineStr">
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>15h 45m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS6" s="2" t="inlineStr">
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:29 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr"/>
+      <c r="V7" s="3" t="inlineStr"/>
+      <c r="W7" s="3" t="inlineStr"/>
+      <c r="X7" s="3" t="inlineStr"/>
+      <c r="Y7" s="3" t="inlineStr"/>
+      <c r="Z7" s="3" t="inlineStr"/>
+      <c r="AA7" s="3" t="inlineStr"/>
+      <c r="AB7" s="3" t="inlineStr"/>
+      <c r="AC7" s="3" t="inlineStr"/>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr"/>
+      <c r="AF7" s="3" t="inlineStr"/>
+      <c r="AG7" s="3" t="inlineStr"/>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr"/>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr"/>
+      <c r="AM7" s="3" t="inlineStr"/>
+      <c r="AN7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr"/>
+      <c r="AP7" s="3" t="inlineStr"/>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX7" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:06 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334079</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Bijaye Subedi</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Bijaye Subedi</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9818937555</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:06:08 AM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9818937555</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 08:17:25 AM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:06:08 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>27.736322</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Near Trijyoti Secondary School P9M6+RX4, Budhanilkantha 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>bdeschopnepal@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>01:06 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>L19-4</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>85.363473</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT6" s="2" t="inlineStr">
-        <is>
-          <t>15h 45m</t>
-        </is>
-      </c>
-      <c r="AU6" s="2" t="inlineStr">
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>2h 48m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV6" s="2" t="inlineStr">
-        <is>
-          <t>Case : wifi 6   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW6" s="2" t="inlineStr">
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX6" s="2" t="inlineStr">
-        <is>
-          <t>Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AY6" s="2" t="b">
-        <v>1</v>
+      <c r="AX8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:28 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>WIFI 6</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1332693</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Girish Ojha</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Girish Ojha</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9823402588</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:28:00 AM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9841501402</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>13 Sep 2026 04:22:39 PM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:28:00 AM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>27.67367</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>Kumari Bank 27.68204, 85.3491, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>workcgnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>11:28 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Sameer Thapa</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>4,10</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr">
+        <is>
+          <t>85.35165</t>
+        </is>
+      </c>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>1d 19h 5m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX9" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:24 AM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : sky com to net tv   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>sky com to net tv</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1333865</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Dolma Lama</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Dolma Lama</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9818723103</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 07:05:43 PM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>9818723103</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 07:05:43 PM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:24:11 AM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr"/>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Near Stupa Butcher Shop, M895+5M5, ?????????? ???, Lalitpur 44700, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr"/>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Replace SKYCOM to NETTV</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr"/>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>2,10</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr"/>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : sky com to net tv   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>16h 18m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>16h 18m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : sky com to net tv   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:22 AM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 router upgrade</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334100</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Abisesh Giri 1</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Abisesh Giri 1</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9822474275</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:22:50 AM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>CHB9822474275</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 09:05:49 AM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:22:50 AM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>Gyaneswor, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>9766847818@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>01:22 hour</t>
+        </is>
+      </c>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>Bhaskar Pant</t>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>CDB497</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr"/>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>2h 17m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX11" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:17 AM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 router upgrade</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334105</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Abhisesh Giri</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Abhisesh Giri</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9766847818</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:17:53 AM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>CHB9766847818</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 09:09:34 AM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:17:53 AM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr"/>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Gyaneshwor, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>Abhiseshgiri1234@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>01:17 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Bhaskar Pant</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>CDB497</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr"/>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>2h 8m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX12" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -676,14 +676,14 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>74.1%</t>
         </is>
       </c>
     </row>
@@ -742,19 +742,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
@@ -765,19 +765,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
@@ -788,19 +788,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>85.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>74.1%</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -889,10 +889,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>0</v>
@@ -904,7 +904,7 @@
         <v>3</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>2</v>
@@ -913,7 +913,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -953,7 +953,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>Low Wi-Fi Range on 5Ghz</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -969,10 +969,10 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>0</v>
@@ -987,7 +987,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Replace SKYCOM to NETTV</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -1019,37 +1019,173 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Other / Uncategorized</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Replace SKYCOM to NETTV</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="C6" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" s="4" t="n">
+      <c r="E10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="F10" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>11</v>
+      <c r="J10" s="4" t="n">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1063,7 +1199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX12"/>
+  <dimension ref="A1:AX28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1074,14 +1210,14 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="27" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="27" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -1091,7 +1227,7 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="25" customWidth="1" min="26" max="26"/>
+    <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
@@ -1103,12 +1239,12 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="26" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="18" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
-    <col width="17" customWidth="1" min="43" max="43"/>
+    <col width="45" customWidth="1" min="43" max="43"/>
     <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
@@ -2575,10 +2711,8 @@
           <t>Bijaye Subedi</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9818937555</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9818937555</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2613,10 +2747,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>27.736322</t>
-        </is>
+      <c r="Y8" s="3" t="n">
+        <v>27.736322</v>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
@@ -2672,25 +2804,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>L19-4</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>85.363473</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>85.363473</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
@@ -2791,10 +2919,8 @@
           <t>Girish Ojha</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9823402588</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9823402588</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2829,10 +2955,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>27.67367</t>
-        </is>
+      <c r="Y9" s="3" t="n">
+        <v>27.67367</v>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
@@ -2888,25 +3012,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
           <t>4,10</t>
         </is>
       </c>
-      <c r="AP9" s="3" t="inlineStr">
-        <is>
-          <t>85.35165</t>
-        </is>
+      <c r="AP9" s="3" t="n">
+        <v>85.35165000000001</v>
       </c>
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
@@ -3007,10 +3127,8 @@
           <t>Dolma Lama</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9818723103</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9818723103</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -3092,10 +3210,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
@@ -3106,7 +3222,7 @@
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>Case : sky com to net tv   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
@@ -3207,10 +3323,8 @@
           <t>Abisesh Giri 1</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9822474275</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9822474275</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -3300,10 +3414,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
@@ -3314,7 +3426,7 @@
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
@@ -3415,10 +3527,8 @@
           <t>Abhisesh Giri</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9766847818</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9766847818</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -3508,10 +3618,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
@@ -3522,37 +3630,3483 @@
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>2h 8m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS12" s="3" t="inlineStr">
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX12" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:34 PM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV blank display  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>IPTV blank display</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334172</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Dil Kumar Shrestha</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Dil Kumar Shrestha</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9842097155</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:34:16 PM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>9842097155</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 09:58:03 AM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:34:16 PM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>27.686495</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>Active English Secondary School Active English Secondary School - High school M9JP+R53 Bhaktapur Roa</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr">
+        <is>
+          <t>damakcadil@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>02:34 hour</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Sanish Magar</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>4,5</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>85.378118</t>
+        </is>
+      </c>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV blank display  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT12" s="3" t="inlineStr">
-        <is>
-          <t>2h 8m</t>
-        </is>
-      </c>
-      <c r="AU12" s="3" t="inlineStr">
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>2h 36m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV12" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="AW12" s="3" t="inlineStr">
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV blank display  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX13" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:47 AM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1333648</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Kushal Neupane</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Kushal Neupane</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9844064169</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:47:26 AM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>9844064169</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 03:17:35 PM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:47:26 AM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t>27.66527</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>Tikathali Bus Stop,Tikathali, Mahalaxmi 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr">
+        <is>
+          <t>kurt.kushal1989@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Remote damage Issue</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr">
+        <is>
+          <t>06:30 hour</t>
+        </is>
+      </c>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr">
+        <is>
+          <t>Prabin Parajuli</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>CDB471</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>85.3599</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>20h 29m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 1:31 PM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 router</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>TKT1333455</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Ranjana jimee</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Ranjana jimee</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>9851150629</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:31:34 PM</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>9856022476</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 12:32:40 PM</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:31:34 PM</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr">
+        <is>
+          <t>27.68817</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr">
+        <is>
+          <t>Box End</t>
+        </is>
+      </c>
+      <c r="AE15" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur,kathmandu,near Gurudwara Guru Nanak Satsang, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="inlineStr">
+        <is>
+          <t>Jimeeranjana@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG15" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr">
+        <is>
+          <t>10:59 hour</t>
+        </is>
+      </c>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr"/>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>CDB506</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr">
+        <is>
+          <t>85.31543</t>
+        </is>
+      </c>
+      <c r="AQ15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu
+(15 Sep 2026 01:31:35 PM) :
+Router has been upgraded
+TKT1333455
+9856022476
+Ranjana jimee
+New SN : ALCLFE4FE240
+Old SN : ALCLB2B212F3
+Note : Upgrade to wifi6
+Remark  
+Document
+Related Documents</t>
+        </is>
+      </c>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu
+(15 Sep 2026 01:31:35 PM) :
+Router has been upgraded
+TKT1333455
+9856022476
+Ranjana jimee
+New SN : ALCLFE4FE240
+Old SN : ALCLB2B212F3
+Note : Upgrade to wifi6
+Remark  
+Document
+Related Documents</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>1d 58m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX12" s="3" t="inlineStr">
+      <c r="AX15" s="3" t="inlineStr">
         <is>
           <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:47 PM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1333363</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Kanunalaya Inc. Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Kanunalaya Inc. Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9851177792</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:47:59 PM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>9851177792</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 11:24:30 AM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:47:59 PM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>27.69393</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>Near Ghostwriting Nepal, Bhadra Vinayak Marga , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr">
+        <is>
+          <t>suneetaraut@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>11:23 hour</t>
+        </is>
+      </c>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>L47-2</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>85.331616</t>
+        </is>
+      </c>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 23m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX16" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:46 PM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Dual band  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Dual band</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334089</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Arun Bhandari</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Follow Up</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Arun Bhandari</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9865297766</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:46:27 PM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>9868297864</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 08:40:37 AM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:46:27 PM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr">
+        <is>
+          <t>27.69864</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>Near Puja Pratisthan ???? ??????????, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr">
+        <is>
+          <t>arunbhandari698@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>02:46 hour</t>
+        </is>
+      </c>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Prabin Parajuli</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>L64-5</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr">
+        <is>
+          <t>85.33317</t>
+        </is>
+      </c>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Dual band  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>4h 5m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Dual band  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX17" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 1:21 PM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : for wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>for wifi 6</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1333526</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Uttam KC</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Uttam KC</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9865667017</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 01:36:58 PM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>9865667017</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 01:34:08 PM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:21:58 PM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr"/>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Near Corona Pre-School, P7GR+8MX, Dhungedhara Road, Nagarjun 44600 - Near Corona Pre-School, P7GR+8M</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr">
+        <is>
+          <t>uttamkc71@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr">
+        <is>
+          <t>09:47 hour</t>
+        </is>
+      </c>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Sitaram Adhikari</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>4,9</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr"/>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case : for wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>23h 45m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>23h 47m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : for wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX18" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:13 PM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1333979</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>lavkush kumar mukhiya</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>lavkush kumar mukhiya</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9762420859</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 09:49:30 PM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>KLK9762420859</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 09:49:30 PM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:13:52 PM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr"/>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>nar by Kumari Club Building - Club Dakchhinkali Road Kathmandu 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr">
+        <is>
+          <t>9851424302@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr">
+        <is>
+          <t>02:13 hour</t>
+        </is>
+      </c>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>CDB022</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr"/>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>14h 24m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>14h 24m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX19" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 1:27 PM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>For upgradation to wifi6</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1333912</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Saroj Karki</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Saroj Karki</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>9869527479</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:27:57 PM</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>KLK9869527479</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 07:56:46 PM</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:27:57 PM</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr"/>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr">
+        <is>
+          <t>Lolang tarakeshwor , Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="inlineStr">
+        <is>
+          <t>123@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG20" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI20" s="3" t="inlineStr">
+        <is>
+          <t>03:31 hour</t>
+        </is>
+      </c>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>L51-3</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr"/>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>17h 31m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX20" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:46 PM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334125</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Niran Shahi Thakuri</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Niran Shahi Thakuri</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9845603766</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:46:14 PM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>9845603766</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 09:28:19 AM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:46:14 PM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr">
+        <is>
+          <t>27.73941</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>Near nagaarjun party place, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr"/>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>02:46 hour</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>CDB046</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr">
+        <is>
+          <t>85.3076</t>
+        </is>
+      </c>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>3h 17m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX21" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:22 PM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334129</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Uday Bhahadur Rana Magar</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Uday Bhahadur Rana Magar</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>9851070038</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:22:18 PM</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>9851070038</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 09:31:27 AM</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:24:45 PM</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr">
+        <is>
+          <t>27.756502</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr">
+        <is>
+          <t>Dhalmal pul baniyatar, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="inlineStr">
+        <is>
+          <t>raamagaruday18@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG22" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr">
+        <is>
+          <t>03:24 hour</t>
+        </is>
+      </c>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t>Sandesh Ghale</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>Binod Dhami</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>L10-3</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr">
+        <is>
+          <t>85.317497</t>
+        </is>
+      </c>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>1h 2m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>3h 53m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX22" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:51 AM</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>TKT1332927</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Madhukar Aryal</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>Madhukar Aryal</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>9860752387</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:51:53 AM</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>9860752387</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>13 Sep 2026 07:29:48 PM</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:51:53 AM</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr">
+        <is>
+          <t>27.755555</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA23" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC23" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr">
+        <is>
+          <t>Rosemary Idol Boarding School - School Q846+3R, 8 Tarakeshwar 44610, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF23" s="3" t="inlineStr">
+        <is>
+          <t>aryalmadhukar@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG23" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr"/>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>L41-8A</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr">
+        <is>
+          <t>85.310901</t>
+        </is>
+      </c>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>1d 16h 22m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX23" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:45 AM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1332927</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Madhukar Aryal</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Madhukar Aryal</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>9860752387</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:51:53 AM</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>9860752387</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>13 Sep 2026 07:29:48 PM</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:51:53 AM</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>27.755555</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr">
+        <is>
+          <t>Rosemary Idol Boarding School - School Q846+3R, 8 Tarakeshwar 44610, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF24" s="3" t="inlineStr">
+        <is>
+          <t>aryalmadhukar@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="3" t="inlineStr"/>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
+          <t>L41-8A</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr">
+        <is>
+          <t>85.310901</t>
+        </is>
+      </c>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>1d 16h 22m</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX24" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 1:08 PM</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334065</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Saradha Panta</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Saradha Panta</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>9851322004</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:08:55 PM</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>9851322004</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 07:57:11 AM</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:08:55 PM</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t>27.71579</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr">
+        <is>
+          <t>Sarveshwor Mahadev Temple, Nayabasti, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF25" s="3" t="inlineStr">
+        <is>
+          <t>workcgnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG25" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr"/>
+      <c r="AI25" s="3" t="inlineStr">
+        <is>
+          <t>03:08 hour</t>
+        </is>
+      </c>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>L31-6</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr">
+        <is>
+          <t>85.36397</t>
+        </is>
+      </c>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>5h 11m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX25" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:35 PM</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334065</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Saradha Panta</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Saradha Panta</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>9851322004</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:08:55 PM</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>9851322004</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 07:57:11 AM</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:08:55 PM</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t>27.71579</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA26" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC26" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD26" s="3" t="inlineStr"/>
+      <c r="AE26" s="3" t="inlineStr">
+        <is>
+          <t>Sarveshwor Mahadev Temple, Nayabasti, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF26" s="3" t="inlineStr">
+        <is>
+          <t>workcgnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG26" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH26" s="3" t="inlineStr"/>
+      <c r="AI26" s="3" t="inlineStr">
+        <is>
+          <t>03:08 hour</t>
+        </is>
+      </c>
+      <c r="AJ26" s="3" t="inlineStr"/>
+      <c r="AK26" s="3" t="inlineStr"/>
+      <c r="AL26" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>L31-6</t>
+        </is>
+      </c>
+      <c r="AP26" s="3" t="inlineStr">
+        <is>
+          <t>85.36397</t>
+        </is>
+      </c>
+      <c r="AQ26" s="3" t="inlineStr"/>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>5h 11m</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW26" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX26" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:40 AM</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334065</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Saradha Panta</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>Saradha Panta</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>9851322004</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:08:55 PM</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>9851322004</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 07:57:11 AM</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:08:55 PM</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr">
+        <is>
+          <t>27.71579</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA27" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC27" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr"/>
+      <c r="AE27" s="3" t="inlineStr">
+        <is>
+          <t>Sarveshwor Mahadev Temple, Nayabasti, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF27" s="3" t="inlineStr">
+        <is>
+          <t>workcgnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG27" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH27" s="3" t="inlineStr"/>
+      <c r="AI27" s="3" t="inlineStr">
+        <is>
+          <t>03:08 hour</t>
+        </is>
+      </c>
+      <c r="AJ27" s="3" t="inlineStr"/>
+      <c r="AK27" s="3" t="inlineStr"/>
+      <c r="AL27" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO27" s="3" t="inlineStr">
+        <is>
+          <t>L31-6</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr">
+        <is>
+          <t>85.36397</t>
+        </is>
+      </c>
+      <c r="AQ27" s="3" t="inlineStr"/>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>5h 11m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW27" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX27" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:38 AM</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>Slow internet</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1333628</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>Biraj poudel</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>Biraj poudel</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>9767216151</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 04:19:35 PM</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>CHB9767216151</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 02:59:37 PM</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:38:26 AM</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="AA28" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB28" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC28" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD28" s="3" t="inlineStr"/>
+      <c r="AE28" s="3" t="inlineStr">
+        <is>
+          <t>27.69999299027229, 85.34332452221567, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF28" s="3" t="inlineStr">
+        <is>
+          <t>9767216151@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG28" s="3" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on 5Ghz</t>
+        </is>
+      </c>
+      <c r="AH28" s="3" t="inlineStr"/>
+      <c r="AI28" s="3" t="inlineStr"/>
+      <c r="AJ28" s="3" t="inlineStr"/>
+      <c r="AK28" s="3" t="inlineStr"/>
+      <c r="AL28" s="3" t="inlineStr">
+        <is>
+          <t>Sandesh Ghale</t>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO28" s="3" t="inlineStr">
+        <is>
+          <t>L36-5</t>
+        </is>
+      </c>
+      <c r="AP28" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ28" s="3" t="inlineStr"/>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>19h 18m</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>20h 38m</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX28" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Sep_2026.xlsx
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>5</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C6" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -676,14 +676,14 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>75.8%</t>
         </is>
       </c>
     </row>
@@ -742,19 +742,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.1%</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>9.1%</t>
         </is>
       </c>
     </row>
@@ -788,19 +788,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>84.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>75.8%</t>
         </is>
       </c>
     </row>
@@ -889,10 +889,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>0</v>
@@ -901,10 +901,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>2</v>
@@ -913,7 +913,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>0</v>
@@ -1173,10 +1173,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H10" s="4" t="n">
         <v>5</v>
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1199,7 +1199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX28"/>
+  <dimension ref="A1:AX34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3731,10 +3731,8 @@
           <t>Dil Kumar Shrestha</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9842097155</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9842097155</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -3769,10 +3767,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y13" s="3" t="inlineStr">
-        <is>
-          <t>27.686495</t>
-        </is>
+      <c r="Y13" s="3" t="n">
+        <v>27.686495</v>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
@@ -3828,25 +3824,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
           <t>4,5</t>
         </is>
       </c>
-      <c r="AP13" s="3" t="inlineStr">
-        <is>
-          <t>85.378118</t>
-        </is>
+      <c r="AP13" s="3" t="n">
+        <v>85.378118</v>
       </c>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV blank display  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
@@ -3947,10 +3939,8 @@
           <t>Kushal Neupane</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9844064169</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9844064169</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3985,10 +3975,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t>27.66527</t>
-        </is>
+      <c r="Y14" s="3" t="n">
+        <v>27.66527</v>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
@@ -4044,25 +4032,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
           <t>CDB471</t>
         </is>
       </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>85.3599</t>
-        </is>
+      <c r="AP14" s="3" t="n">
+        <v>85.3599</v>
       </c>
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
@@ -4163,10 +4147,8 @@
           <t>Ranjana jimee</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>9851150629</t>
-        </is>
+      <c r="O15" s="3" t="n">
+        <v>9851150629</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
@@ -4201,10 +4183,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y15" s="3" t="inlineStr">
-        <is>
-          <t>27.68817</t>
-        </is>
+      <c r="Y15" s="3" t="n">
+        <v>27.68817</v>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
@@ -4260,20 +4240,16 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN15" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
           <t>CDB506</t>
         </is>
       </c>
-      <c r="AP15" s="3" t="inlineStr">
-        <is>
-          <t>85.31543</t>
-        </is>
+      <c r="AP15" s="3" t="n">
+        <v>85.31543000000001</v>
       </c>
       <c r="AQ15" s="3" t="inlineStr">
         <is>
@@ -4405,10 +4381,8 @@
           <t>Kanunalaya Inc. Pvt Ltd</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9851177792</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9851177792</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -4443,10 +4417,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y16" s="3" t="inlineStr">
-        <is>
-          <t>27.69393</t>
-        </is>
+      <c r="Y16" s="3" t="n">
+        <v>27.69393</v>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
@@ -4502,25 +4474,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
           <t>L47-2</t>
         </is>
       </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>85.331616</t>
-        </is>
+      <c r="AP16" s="3" t="n">
+        <v>85.331616</v>
       </c>
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
@@ -4621,10 +4589,8 @@
           <t>Arun Bhandari</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9865297766</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9865297766</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -4659,10 +4625,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y17" s="3" t="inlineStr">
-        <is>
-          <t>27.69864</t>
-        </is>
+      <c r="Y17" s="3" t="n">
+        <v>27.69864</v>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
@@ -4718,25 +4682,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
           <t>L64-5</t>
         </is>
       </c>
-      <c r="AP17" s="3" t="inlineStr">
-        <is>
-          <t>85.33317</t>
-        </is>
+      <c r="AP17" s="3" t="n">
+        <v>85.33317</v>
       </c>
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>Case : Dual band  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
@@ -4837,10 +4797,8 @@
           <t>Uttam KC</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9865667017</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9865667017</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -4930,10 +4888,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
@@ -4944,7 +4900,7 @@
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>Case : for wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
@@ -5045,10 +5001,8 @@
           <t>lavkush kumar mukhiya</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9762420859</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9762420859</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -5138,10 +5092,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
@@ -5152,7 +5104,7 @@
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
@@ -5243,20 +5195,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M20" s="3" t="inlineStr"/>
       <c r="N20" s="3" t="inlineStr">
         <is>
           <t>Saroj Karki</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>9869527479</t>
-        </is>
+      <c r="O20" s="3" t="n">
+        <v>9869527479</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -5328,10 +5274,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH20" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH20" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI20" s="3" t="inlineStr">
         <is>
@@ -5350,10 +5294,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN20" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
@@ -5364,7 +5306,7 @@
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
@@ -5465,10 +5407,8 @@
           <t>Niran Shahi Thakuri</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9845603766</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9845603766</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -5503,10 +5443,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y21" s="3" t="inlineStr">
-        <is>
-          <t>27.73941</t>
-        </is>
+      <c r="Y21" s="3" t="n">
+        <v>27.73941</v>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
@@ -5558,25 +5496,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
           <t>CDB046</t>
         </is>
       </c>
-      <c r="AP21" s="3" t="inlineStr">
-        <is>
-          <t>85.3076</t>
-        </is>
+      <c r="AP21" s="3" t="n">
+        <v>85.30759999999999</v>
       </c>
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
@@ -5677,10 +5611,8 @@
           <t>Uday Bhahadur Rana Magar</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>9851070038</t>
-        </is>
+      <c r="O22" s="3" t="n">
+        <v>9851070038</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -5715,10 +5647,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y22" s="3" t="inlineStr">
-        <is>
-          <t>27.756502</t>
-        </is>
+      <c r="Y22" s="3" t="n">
+        <v>27.756502</v>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
@@ -5774,25 +5704,21 @@
           <t>Binod Dhami</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN22" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
           <t>L10-3</t>
         </is>
       </c>
-      <c r="AP22" s="3" t="inlineStr">
-        <is>
-          <t>85.317497</t>
-        </is>
+      <c r="AP22" s="3" t="n">
+        <v>85.317497</v>
       </c>
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
@@ -5893,10 +5819,8 @@
           <t>Madhukar Aryal</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>9860752387</t>
-        </is>
+      <c r="O23" s="3" t="n">
+        <v>9860752387</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
@@ -5931,10 +5855,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y23" s="3" t="inlineStr">
-        <is>
-          <t>27.755555</t>
-        </is>
+      <c r="Y23" s="3" t="n">
+        <v>27.755555</v>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
@@ -5986,25 +5908,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN23" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
           <t>L41-8A</t>
         </is>
       </c>
-      <c r="AP23" s="3" t="inlineStr">
-        <is>
-          <t>85.310901</t>
-        </is>
+      <c r="AP23" s="3" t="n">
+        <v>85.310901</v>
       </c>
       <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
@@ -6105,10 +6023,8 @@
           <t>Madhukar Aryal</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>9860752387</t>
-        </is>
+      <c r="O24" s="3" t="n">
+        <v>9860752387</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
@@ -6143,10 +6059,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t>27.755555</t>
-        </is>
+      <c r="Y24" s="3" t="n">
+        <v>27.755555</v>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
@@ -6198,25 +6112,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN24" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
           <t>L41-8A</t>
         </is>
       </c>
-      <c r="AP24" s="3" t="inlineStr">
-        <is>
-          <t>85.310901</t>
-        </is>
+      <c r="AP24" s="3" t="n">
+        <v>85.310901</v>
       </c>
       <c r="AQ24" s="3" t="inlineStr"/>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
@@ -6317,10 +6227,8 @@
           <t>Saradha Panta</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>9851322004</t>
-        </is>
+      <c r="O25" s="3" t="n">
+        <v>9851322004</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
@@ -6355,10 +6263,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t>27.71579</t>
-        </is>
+      <c r="Y25" s="3" t="n">
+        <v>27.71579</v>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
@@ -6414,25 +6320,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN25" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
           <t>L31-6</t>
         </is>
       </c>
-      <c r="AP25" s="3" t="inlineStr">
-        <is>
-          <t>85.36397</t>
-        </is>
+      <c r="AP25" s="3" t="n">
+        <v>85.36396999999999</v>
       </c>
       <c r="AQ25" s="3" t="inlineStr"/>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
@@ -6533,10 +6435,8 @@
           <t>Saradha Panta</t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>9851322004</t>
-        </is>
+      <c r="O26" s="3" t="n">
+        <v>9851322004</v>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
@@ -6571,10 +6471,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y26" s="3" t="inlineStr">
-        <is>
-          <t>27.71579</t>
-        </is>
+      <c r="Y26" s="3" t="n">
+        <v>27.71579</v>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
@@ -6630,25 +6528,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN26" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
           <t>L31-6</t>
         </is>
       </c>
-      <c r="AP26" s="3" t="inlineStr">
-        <is>
-          <t>85.36397</t>
-        </is>
+      <c r="AP26" s="3" t="n">
+        <v>85.36396999999999</v>
       </c>
       <c r="AQ26" s="3" t="inlineStr"/>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
@@ -6749,10 +6643,8 @@
           <t>Saradha Panta</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>9851322004</t>
-        </is>
+      <c r="O27" s="3" t="n">
+        <v>9851322004</v>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
@@ -6787,10 +6679,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y27" s="3" t="inlineStr">
-        <is>
-          <t>27.71579</t>
-        </is>
+      <c r="Y27" s="3" t="n">
+        <v>27.71579</v>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
@@ -6846,25 +6736,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN27" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
           <t>L31-6</t>
         </is>
       </c>
-      <c r="AP27" s="3" t="inlineStr">
-        <is>
-          <t>85.36397</t>
-        </is>
+      <c r="AP27" s="3" t="n">
+        <v>85.36396999999999</v>
       </c>
       <c r="AQ27" s="3" t="inlineStr"/>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
@@ -6965,10 +6851,8 @@
           <t>Biraj poudel</t>
         </is>
       </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>9767216151</t>
-        </is>
+      <c r="O28" s="3" t="n">
+        <v>9767216151</v>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
@@ -7003,10 +6887,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y28" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
@@ -7058,55 +6940,1335 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN28" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
           <t>L36-5</t>
         </is>
       </c>
-      <c r="AP28" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ28" s="3" t="inlineStr"/>
       <c r="AR28" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>19h 18m</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>20h 38m</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
           <t>Case : Slow internet  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS28" s="3" t="inlineStr">
-        <is>
-          <t>19h 18m</t>
-        </is>
-      </c>
-      <c r="AT28" s="3" t="inlineStr">
-        <is>
-          <t>20h 38m</t>
-        </is>
-      </c>
-      <c r="AU28" s="3" t="inlineStr">
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX28" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 2:01 PM</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>TKT1333868</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>Ganesh Lal Gurung</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>Ganesh Lal Gurung</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>9848326369</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:01:58 PM</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>9848326369</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 07:06:45 PM</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:01:58 PM</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr">
+        <is>
+          <t>27.7327</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA29" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC29" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD29" s="3" t="inlineStr"/>
+      <c r="AE29" s="3" t="inlineStr">
+        <is>
+          <t>Near Middle Orbit Overseas Pvt. Ltd., P8M9+588, Kathmandu 44611, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF29" s="3" t="inlineStr">
+        <is>
+          <t>ganesh@laundryunion.com</t>
+        </is>
+      </c>
+      <c r="AG29" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH29" s="3" t="inlineStr"/>
+      <c r="AI29" s="3" t="inlineStr">
+        <is>
+          <t>04:55 hour</t>
+        </is>
+      </c>
+      <c r="AJ29" s="3" t="inlineStr"/>
+      <c r="AK29" s="3" t="inlineStr"/>
+      <c r="AL29" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO29" s="3" t="inlineStr">
+        <is>
+          <t>2,6</t>
+        </is>
+      </c>
+      <c r="AP29" s="3" t="inlineStr">
+        <is>
+          <t>85.3181</t>
+        </is>
+      </c>
+      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>18h 55m</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW29" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX29" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 2:26 PM</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1333879</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>Rekha rawat</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Rekha rawat</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>9863329493</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:26:01 PM</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>9863329493</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 07:20:59 PM</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:26:01 PM</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr"/>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA30" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC30" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD30" s="3" t="inlineStr"/>
+      <c r="AE30" s="3" t="inlineStr">
+        <is>
+          <t>27.686798646165148, 85.2887221697945, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="inlineStr"/>
+      <c r="AG30" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH30" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI30" s="3" t="inlineStr"/>
+      <c r="AJ30" s="3" t="inlineStr"/>
+      <c r="AK30" s="3" t="inlineStr"/>
+      <c r="AL30" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO30" s="3" t="inlineStr">
+        <is>
+          <t>1,12</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr"/>
+      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>19h 5m</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
         <is>
           <t>Other / In Progress (On Hold)</t>
         </is>
       </c>
-      <c r="AV28" s="3" t="inlineStr">
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX30" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 2:26 PM</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>Case : Slow internet  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AW28" s="3" t="inlineStr">
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>Slow internet</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>TKT1333628</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>Biraj poudel</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>Biraj poudel</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>9767216151</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:26:43 PM</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>CHB9767216151</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 02:59:37 PM</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:26:43 PM</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y31" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="AA31" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC31" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD31" s="3" t="inlineStr"/>
+      <c r="AE31" s="3" t="inlineStr">
+        <is>
+          <t>27.69999299027229, 85.34332452221567, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF31" s="3" t="inlineStr">
+        <is>
+          <t>9767216151@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG31" s="3" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on 5Ghz</t>
+        </is>
+      </c>
+      <c r="AH31" s="3" t="inlineStr"/>
+      <c r="AI31" s="3" t="inlineStr">
+        <is>
+          <t>09:27 hour</t>
+        </is>
+      </c>
+      <c r="AJ31" s="3" t="inlineStr"/>
+      <c r="AK31" s="3" t="inlineStr"/>
+      <c r="AL31" s="3" t="inlineStr">
+        <is>
+          <t>Sandesh Ghale</t>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO31" s="3" t="inlineStr">
+        <is>
+          <t>L36-5</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>23h 27m</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW31" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AX28" s="3" t="inlineStr">
+      <c r="AX31" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 1:39 PM</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334223</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Srijana Magar</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Srijana Magar</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>9808791830</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:39:14 PM</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>9808791830</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:26:08 AM</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:50:45 PM</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t>27.73618</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA32" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC32" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD32" s="3" t="inlineStr"/>
+      <c r="AE32" s="3" t="inlineStr">
+        <is>
+          <t>Tudaldevi Marg,Tudaldevi Temple, Kathmandu,, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF32" s="3" t="inlineStr">
+        <is>
+          <t>bjp.thito@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH32" s="3" t="inlineStr"/>
+      <c r="AI32" s="3" t="inlineStr">
+        <is>
+          <t>03:13 hour</t>
+        </is>
+      </c>
+      <c r="AJ32" s="3" t="inlineStr"/>
+      <c r="AK32" s="3" t="inlineStr"/>
+      <c r="AL32" s="3" t="inlineStr">
+        <is>
+          <t>Indra KC</t>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>Rahul Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>L21-2</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr">
+        <is>
+          <t>85.32829</t>
+        </is>
+      </c>
+      <c r="AQ32" s="3" t="inlineStr"/>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>11m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>3h 24m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW32" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX32" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 2:17 PM</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>TKT1333699</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>Lok Parsad Silwal</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>Lok Parsad Silwal</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>9851022984</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 03:49:03 PM</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>9851022984</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 03:49:03 PM</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:17:52 PM</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr">
+        <is>
+          <t>27.70788</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA33" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB33" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC33" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr"/>
+      <c r="AE33" s="3" t="inlineStr">
+        <is>
+          <t>Near Ratna Store, Chhauni, Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF33" s="3" t="inlineStr">
+        <is>
+          <t>nepaltravellink@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG33" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH33" s="3" t="inlineStr"/>
+      <c r="AI33" s="3" t="inlineStr">
+        <is>
+          <t>08:28 hour</t>
+        </is>
+      </c>
+      <c r="AJ33" s="3" t="inlineStr"/>
+      <c r="AK33" s="3" t="inlineStr"/>
+      <c r="AL33" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>CDB384</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>85.29744</t>
+        </is>
+      </c>
+      <c r="AQ33" s="3" t="inlineStr"/>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>22h 28m</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>22h 28m</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW33" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX33" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 1:57 PM</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334316</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Rama Shrestha</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Rama Shrestha</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>9813456223</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:15:01 AM</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>9880059826</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:15:01 AM</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:57:47 PM</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y34" s="3" t="inlineStr">
+        <is>
+          <t>27.71182</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA34" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC34" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="inlineStr"/>
+      <c r="AE34" s="3" t="inlineStr">
+        <is>
+          <t>Near Little Buddha's Academy,Bijeshowri, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="inlineStr">
+        <is>
+          <t>rawmaashrestha456@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr"/>
+      <c r="AI34" s="3" t="inlineStr">
+        <is>
+          <t>02:42 hour</t>
+        </is>
+      </c>
+      <c r="AJ34" s="3" t="inlineStr"/>
+      <c r="AK34" s="3" t="inlineStr"/>
+      <c r="AL34" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>CDB248</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr">
+        <is>
+          <t>85.29671</t>
+        </is>
+      </c>
+      <c r="AQ34" s="3" t="inlineStr"/>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>2h 42m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>2h 42m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX34" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Sep_2026.xlsx
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C8" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -676,14 +676,14 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>75.8%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>8.3%</t>
         </is>
       </c>
     </row>
@@ -788,19 +788,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>84.0%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>75.8%</t>
+          <t>72.2%</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>5</v>
@@ -907,13 +907,13 @@
         <v>6</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -953,7 +953,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on 5Ghz</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -969,13 +969,13 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0</v>
@@ -987,7 +987,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -1006,10 +1006,10 @@
         <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>Low Wi-Fi Range on 5Ghz</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -1037,10 +1037,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>0</v>
@@ -1089,14 +1089,14 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>
@@ -1123,14 +1123,14 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Blank TV Display</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0</v>
@@ -1145,7 +1145,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>0</v>
@@ -1155,37 +1155,71 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C10" s="4" t="n">
+      <c r="B11" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F11" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="H10" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="I10" s="4" t="n">
+      <c r="H11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="I11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="4" t="n">
-        <v>28</v>
+      <c r="J11" s="4" t="n">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1199,7 +1233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX34"/>
+  <dimension ref="A1:AX37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -7055,10 +7089,8 @@
           <t>Ganesh Lal Gurung</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>9848326369</t>
-        </is>
+      <c r="O29" s="3" t="n">
+        <v>9848326369</v>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
@@ -7093,10 +7125,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y29" s="3" t="inlineStr">
-        <is>
-          <t>27.7327</t>
-        </is>
+      <c r="Y29" s="3" t="n">
+        <v>27.7327</v>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
@@ -7152,25 +7182,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN29" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN29" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
           <t>2,6</t>
         </is>
       </c>
-      <c r="AP29" s="3" t="inlineStr">
-        <is>
-          <t>85.3181</t>
-        </is>
+      <c r="AP29" s="3" t="n">
+        <v>85.3181</v>
       </c>
       <c r="AQ29" s="3" t="inlineStr"/>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
@@ -7271,10 +7297,8 @@
           <t>Rekha rawat</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>9863329493</t>
-        </is>
+      <c r="O30" s="3" t="n">
+        <v>9863329493</v>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
@@ -7342,10 +7366,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH30" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH30" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI30" s="3" t="inlineStr"/>
       <c r="AJ30" s="3" t="inlineStr"/>
@@ -7360,10 +7382,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN30" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
@@ -7374,7 +7394,7 @@
       <c r="AQ30" s="3" t="inlineStr"/>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
@@ -7475,10 +7495,8 @@
           <t>Biraj poudel</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>9767216151</t>
-        </is>
+      <c r="O31" s="3" t="n">
+        <v>9767216151</v>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
@@ -7513,10 +7531,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y31" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y31" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
@@ -7572,25 +7588,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN31" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
           <t>L36-5</t>
         </is>
       </c>
-      <c r="AP31" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP31" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ31" s="3" t="inlineStr"/>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>Case : Slow internet  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
@@ -7691,10 +7703,8 @@
           <t>Srijana Magar</t>
         </is>
       </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>9808791830</t>
-        </is>
+      <c r="O32" s="3" t="n">
+        <v>9808791830</v>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
@@ -7729,10 +7739,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y32" s="3" t="inlineStr">
-        <is>
-          <t>27.73618</t>
-        </is>
+      <c r="Y32" s="3" t="n">
+        <v>27.73618</v>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
@@ -7788,25 +7796,21 @@
           <t>Rahul Chaudhary</t>
         </is>
       </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN32" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
           <t>L21-2</t>
         </is>
       </c>
-      <c r="AP32" s="3" t="inlineStr">
-        <is>
-          <t>85.32829</t>
-        </is>
+      <c r="AP32" s="3" t="n">
+        <v>85.32829</v>
       </c>
       <c r="AQ32" s="3" t="inlineStr"/>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
@@ -7907,10 +7911,8 @@
           <t>Lok Parsad Silwal</t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>9851022984</t>
-        </is>
+      <c r="O33" s="3" t="n">
+        <v>9851022984</v>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
@@ -7945,10 +7947,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y33" s="3" t="inlineStr">
-        <is>
-          <t>27.70788</t>
-        </is>
+      <c r="Y33" s="3" t="n">
+        <v>27.70788</v>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
@@ -8004,25 +8004,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN33" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
           <t>CDB384</t>
         </is>
       </c>
-      <c r="AP33" s="3" t="inlineStr">
-        <is>
-          <t>85.29744</t>
-        </is>
+      <c r="AP33" s="3" t="n">
+        <v>85.29743999999999</v>
       </c>
       <c r="AQ33" s="3" t="inlineStr"/>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
@@ -8123,10 +8119,8 @@
           <t>Rama Shrestha</t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>9813456223</t>
-        </is>
+      <c r="O34" s="3" t="n">
+        <v>9813456223</v>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
@@ -8161,10 +8155,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y34" s="3" t="inlineStr">
-        <is>
-          <t>27.71182</t>
-        </is>
+      <c r="Y34" s="3" t="n">
+        <v>27.71182</v>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
@@ -8220,55 +8212,679 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN34" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
           <t>CDB248</t>
         </is>
       </c>
-      <c r="AP34" s="3" t="inlineStr">
-        <is>
-          <t>85.29671</t>
-        </is>
+      <c r="AP34" s="3" t="n">
+        <v>85.29671</v>
       </c>
       <c r="AQ34" s="3" t="inlineStr"/>
       <c r="AR34" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>2h 42m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>2h 42m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS34" s="3" t="inlineStr">
-        <is>
-          <t>2h 42m</t>
-        </is>
-      </c>
-      <c r="AT34" s="3" t="inlineStr">
-        <is>
-          <t>2h 42m</t>
-        </is>
-      </c>
-      <c r="AU34" s="3" t="inlineStr">
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX34" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 2:46 PM</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>TKT1333643</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Manish Agrawal</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>Manish Agrawal</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>9851182604</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 03:15:17 PM</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t>9851182604</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 03:15:17 PM</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:46:25 PM</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr"/>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA35" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB35" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC35" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="inlineStr"/>
+      <c r="AE35" s="3" t="inlineStr">
+        <is>
+          <t>Sanskar Shikshyalaya - Preschool Tahachal Marg Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF35" s="3" t="inlineStr">
+        <is>
+          <t>memanishktm125@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG35" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH35" s="3" t="inlineStr"/>
+      <c r="AI35" s="3" t="inlineStr">
+        <is>
+          <t>09:31 hour</t>
+        </is>
+      </c>
+      <c r="AJ35" s="3" t="inlineStr"/>
+      <c r="AK35" s="3" t="inlineStr"/>
+      <c r="AL35" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO35" s="3" t="inlineStr">
+        <is>
+          <t>2,3</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr"/>
+      <c r="AQ35" s="3" t="inlineStr"/>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>23h 31m</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>23h 31m</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="AV34" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="AW34" s="3" t="inlineStr">
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX35" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 2:52 PM</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>no light blinking</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334567</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>kshitij kafle</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>kshitij kafle</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>9814791201</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:43:02 PM</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t>BKT9814791201</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:39:20 PM</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:52:13 PM</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr"/>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA36" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC36" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD36" s="3" t="inlineStr"/>
+      <c r="AE36" s="3" t="inlineStr">
+        <is>
+          <t>27.65607,85.37356, Bhaktapur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF36" s="3" t="inlineStr">
+        <is>
+          <t>kshitijkafle21@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG36" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH36" s="3" t="inlineStr"/>
+      <c r="AI36" s="3" t="inlineStr"/>
+      <c r="AJ36" s="3" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr"/>
+      <c r="AL36" s="3" t="inlineStr">
+        <is>
+          <t>Manisha kunwar</t>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO36" s="3" t="inlineStr">
+        <is>
+          <t>4,4</t>
+        </is>
+      </c>
+      <c r="AP36" s="3" t="inlineStr"/>
+      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>1h 9m</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>1h 12m</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX36" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 2:47 PM</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334492</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Dipak Kumar Karki</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>Dipak Kumar Karki</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>9845130442</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:47:15 PM</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr"/>
+      <c r="T37" s="3" t="inlineStr"/>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>9851079644</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:43:35 PM</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:47:15 PM</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="inlineStr">
+        <is>
+          <t>27.67179</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA37" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC37" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="inlineStr"/>
+      <c r="AE37" s="3" t="inlineStr">
+        <is>
+          <t>Narephate ward no:32, Kotdevi marg, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF37" s="3" t="inlineStr">
+        <is>
+          <t>sudhapolyclinic@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG37" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr"/>
+      <c r="AI37" s="3" t="inlineStr">
+        <is>
+          <t>02:04 hour</t>
+        </is>
+      </c>
+      <c r="AJ37" s="3" t="inlineStr"/>
+      <c r="AK37" s="3" t="inlineStr"/>
+      <c r="AL37" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>CDB555</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr">
+        <is>
+          <t>85.34593</t>
+        </is>
+      </c>
+      <c r="AQ37" s="3" t="inlineStr"/>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>2h 3m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW37" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX34" s="3" t="inlineStr">
-        <is>
-          <t>Ajit Shrestha</t>
+      <c r="AX37" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Sep_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
@@ -550,57 +550,57 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Om Neupane</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Rajesh Maharjan</t>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Sabin Giri</t>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -616,74 +616,20 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>71.4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>👥 GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>75.0%</t>
+      <c r="B7" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>76.1%</t>
         </is>
       </c>
     </row>
@@ -742,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>15.2%</t>
         </is>
       </c>
     </row>
@@ -765,19 +711,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>10.9%</t>
         </is>
       </c>
     </row>
@@ -788,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>84.8%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>71.7%</t>
         </is>
       </c>
     </row>
@@ -815,19 +761,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="39" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -848,35 +791,20 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>Om Neupane</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>Rajesh Maharjan</t>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>Sabin Giri</t>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -889,44 +817,35 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G2" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="6" t="n">
-        <v>23</v>
+      <c r="G2" s="6" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Fiber wire breakage suspect</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>0</v>
@@ -935,32 +854,23 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Fiber wire breakage suspect</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>0</v>
@@ -971,23 +881,14 @@
       <c r="F4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="6" t="n">
+      <c r="G4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -1003,18 +904,9 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="6" t="n">
+      <c r="G5" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1031,24 +923,15 @@
         <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="6" t="n">
+      <c r="G6" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1071,25 +954,16 @@
         <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="6" t="n">
+      <c r="G7" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
@@ -1102,35 +976,26 @@
         <v>0</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="6" t="n">
+      <c r="G8" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0</v>
@@ -1139,32 +1004,23 @@
         <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Blank TV Display</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0</v>
@@ -1175,51 +1031,83 @@
       <c r="F10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="6" t="n">
+      <c r="G10" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B13" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="C11" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="4" t="n">
-        <v>31</v>
+      <c r="E13" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1233,7 +1121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX37"/>
+  <dimension ref="A1:AX47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1263,17 +1151,17 @@
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
-    <col width="17" customWidth="1" min="28" max="28"/>
+    <col width="28" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
     <col width="32" customWidth="1" min="32" max="32"/>
-    <col width="30" customWidth="1" min="33" max="33"/>
+    <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="26" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="19" customWidth="1" min="38" max="38"/>
+    <col width="28" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -8327,10 +8215,8 @@
           <t>Manish Agrawal</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>9851182604</t>
-        </is>
+      <c r="O35" s="3" t="n">
+        <v>9851182604</v>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
@@ -8420,10 +8306,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN35" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
@@ -8434,7 +8318,7 @@
       <c r="AQ35" s="3" t="inlineStr"/>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
@@ -8535,10 +8419,8 @@
           <t>kshitij kafle</t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t>9814791201</t>
-        </is>
+      <c r="O36" s="3" t="n">
+        <v>9814791201</v>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
@@ -8624,10 +8506,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN36" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
@@ -8638,7 +8518,7 @@
       <c r="AQ36" s="3" t="inlineStr"/>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
@@ -8739,10 +8619,8 @@
           <t>Dipak Kumar Karki</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>9845130442</t>
-        </is>
+      <c r="O37" s="3" t="n">
+        <v>9845130442</v>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
@@ -8777,10 +8655,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y37" s="3" t="inlineStr">
-        <is>
-          <t>27.67179</t>
-        </is>
+      <c r="Y37" s="3" t="n">
+        <v>27.67179</v>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
@@ -8836,55 +8712,2199 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN37" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
           <t>CDB555</t>
         </is>
       </c>
-      <c r="AP37" s="3" t="inlineStr">
-        <is>
-          <t>85.34593</t>
-        </is>
+      <c r="AP37" s="3" t="n">
+        <v>85.34593</v>
       </c>
       <c r="AQ37" s="3" t="inlineStr"/>
       <c r="AR37" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>2h 3m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS37" s="3" t="inlineStr">
+      <c r="AW37" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX37" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 3:01 PM</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : Iptv issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>Iptv issue</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334031</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>Gautam shrestha</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>Gautam shrestha</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>9851059167</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr"/>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:01:53 PM</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr"/>
+      <c r="T38" s="3" t="inlineStr"/>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>9851059167</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 06:10:23 AM</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:01:53 PM</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr">
+        <is>
+          <t>27.742284</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA38" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB38" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC38" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD38" s="3" t="inlineStr"/>
+      <c r="AE38" s="3" t="inlineStr">
+        <is>
+          <t>Gongabu Bandari tole numble boarding, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF38" s="3" t="inlineStr"/>
+      <c r="AG38" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
+        </is>
+      </c>
+      <c r="AH38" s="3" t="inlineStr"/>
+      <c r="AI38" s="3" t="inlineStr">
+        <is>
+          <t>05:01 hour</t>
+        </is>
+      </c>
+      <c r="AJ38" s="3" t="inlineStr"/>
+      <c r="AK38" s="3" t="inlineStr"/>
+      <c r="AL38" s="3" t="inlineStr">
+        <is>
+          <t>Bishwojeet Adhikari</t>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO38" s="3" t="inlineStr">
+        <is>
+          <t>L61-3</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr">
+        <is>
+          <t>85.316966</t>
+        </is>
+      </c>
+      <c r="AQ38" s="3" t="inlineStr"/>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>Case : Iptv issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT37" s="3" t="inlineStr">
-        <is>
-          <t>2h 3m</t>
-        </is>
-      </c>
-      <c r="AU37" s="3" t="inlineStr">
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>8h 51m</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV37" s="3" t="inlineStr">
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
+          <t>Case : Iptv issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW38" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX38" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 3:58 PM</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334441</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>Sunshine Tradelink</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>Follow Up</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>Sunshine Tradelink</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>9851015418</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:58:40 PM</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr"/>
+      <c r="T39" s="3" t="inlineStr"/>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t>9851015418</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:14:10 PM</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:58:40 PM</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr">
+        <is>
+          <t>27.718612</t>
+        </is>
+      </c>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA39" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB39" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC39" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD39" s="3" t="inlineStr"/>
+      <c r="AE39" s="3" t="inlineStr">
+        <is>
+          <t>Lainchaur Marg, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF39" s="3" t="inlineStr"/>
+      <c r="AG39" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH39" s="3" t="inlineStr"/>
+      <c r="AI39" s="3" t="inlineStr">
+        <is>
+          <t>03:44 hour</t>
+        </is>
+      </c>
+      <c r="AJ39" s="3" t="inlineStr"/>
+      <c r="AK39" s="3" t="inlineStr"/>
+      <c r="AL39" s="3" t="inlineStr">
+        <is>
+          <t>Kusum Gurung</t>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO39" s="3" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="AP39" s="3" t="inlineStr">
+        <is>
+          <t>85.315203</t>
+        </is>
+      </c>
+      <c r="AQ39" s="3" t="inlineStr"/>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>3h 44m</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW39" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX39" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 3:57 PM</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334146</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>Ajib Shrestha</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>Ajib Shrestha</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>9808961772</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr"/>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:57:42 PM</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr"/>
+      <c r="T40" s="3" t="inlineStr"/>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t>9808961772</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 09:43:57 AM</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:57:42 PM</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y40" s="3" t="inlineStr">
+        <is>
+          <t>27.70676</t>
+        </is>
+      </c>
+      <c r="Z40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA40" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB40" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC40" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD40" s="3" t="inlineStr"/>
+      <c r="AE40" s="3" t="inlineStr">
+        <is>
+          <t>Shovabhagwati -15, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF40" s="3" t="inlineStr">
+        <is>
+          <t>ajib.she.50@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG40" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH40" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI40" s="3" t="inlineStr">
+        <is>
+          <t>05:57 hour</t>
+        </is>
+      </c>
+      <c r="AJ40" s="3" t="inlineStr"/>
+      <c r="AK40" s="3" t="inlineStr"/>
+      <c r="AL40" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM40" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN40" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO40" s="3" t="inlineStr">
+        <is>
+          <t>3,6</t>
+        </is>
+      </c>
+      <c r="AP40" s="3" t="inlineStr">
+        <is>
+          <t>85.29837</t>
+        </is>
+      </c>
+      <c r="AQ40" s="3" t="inlineStr"/>
+      <c r="AR40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>6h 13m</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW40" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX40" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 3:15 PM</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334668</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>Manisha Tamrakar</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>Manisha Tamrakar</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>9851075215</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr"/>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:40:42 PM</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="inlineStr"/>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t>9843637315</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:27:57 PM</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:40:42 PM</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y41" s="3" t="inlineStr">
+        <is>
+          <t>27.7126</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA41" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB41" s="3" t="inlineStr">
+        <is>
+          <t>customer experience sales</t>
+        </is>
+      </c>
+      <c r="AC41" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD41" s="3" t="inlineStr"/>
+      <c r="AE41" s="3" t="inlineStr">
+        <is>
+          <t>Swoyambhu Dallu  ward no:15 near Shree Jal Ganesh Pasa Pucha Saving &amp; Credit Co-operative Ltd., Bagm</t>
+        </is>
+      </c>
+      <c r="AF41" s="3" t="inlineStr">
+        <is>
+          <t>asinam3@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG41" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH41" s="3" t="inlineStr"/>
+      <c r="AI41" s="3" t="inlineStr"/>
+      <c r="AJ41" s="3" t="inlineStr"/>
+      <c r="AK41" s="3" t="inlineStr"/>
+      <c r="AL41" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM41" s="3" t="inlineStr">
+        <is>
+          <t>Rikesh Shrestha</t>
+        </is>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO41" s="3" t="inlineStr">
+        <is>
+          <t>1,7</t>
+        </is>
+      </c>
+      <c r="AP41" s="3" t="inlineStr">
+        <is>
+          <t>85.30076</t>
+        </is>
+      </c>
+      <c r="AQ41" s="3" t="inlineStr"/>
+      <c r="AR41" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>1h 12m</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV41" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW41" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX41" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 3:57 PM</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AW37" s="3" t="inlineStr">
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334656</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>Ashok Budal</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>Ashok Budal</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>9848400804</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr"/>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:57:31 PM</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr"/>
+      <c r="T42" s="3" t="inlineStr"/>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t>9848400804</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:18:04 PM</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:57:31 PM</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y42" s="3" t="inlineStr">
+        <is>
+          <t>27.687</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA42" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB42" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC42" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD42" s="3" t="inlineStr"/>
+      <c r="AE42" s="3" t="inlineStr">
+        <is>
+          <t>Near Treasure Music Store,Santinagar,Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF42" s="3" t="inlineStr">
+        <is>
+          <t>ashok.budal1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG42" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH42" s="3" t="inlineStr"/>
+      <c r="AI42" s="3" t="inlineStr">
+        <is>
+          <t>01:39 hour</t>
+        </is>
+      </c>
+      <c r="AJ42" s="3" t="inlineStr"/>
+      <c r="AK42" s="3" t="inlineStr"/>
+      <c r="AL42" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM42" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN42" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO42" s="3" t="inlineStr">
+        <is>
+          <t>L17-5</t>
+        </is>
+      </c>
+      <c r="AP42" s="3" t="inlineStr">
+        <is>
+          <t>85.34223</t>
+        </is>
+      </c>
+      <c r="AQ42" s="3" t="inlineStr"/>
+      <c r="AR42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>1h 39m</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW42" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX37" s="3" t="inlineStr">
+      <c r="AX42" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 3:23 PM</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv setbox issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>iptv setbox issue</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334472</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>Pramod Dhungel</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>Pramod Dhungel</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>9865072901</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:23:50 PM</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>9865072901</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:28:17 PM</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:23:50 PM</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y43" s="3" t="inlineStr">
+        <is>
+          <t>27.6962</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA43" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB43" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC43" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD43" s="3" t="inlineStr"/>
+      <c r="AE43" s="3" t="inlineStr">
+        <is>
+          <t>P98F+FPW, Gokarneshwor 44600,kATHMANDU, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF43" s="3" t="inlineStr">
+        <is>
+          <t>dhungelpramod05@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG43" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH43" s="3" t="inlineStr"/>
+      <c r="AI43" s="3" t="inlineStr">
+        <is>
+          <t>02:55 hour</t>
+        </is>
+      </c>
+      <c r="AJ43" s="3" t="inlineStr"/>
+      <c r="AK43" s="3" t="inlineStr"/>
+      <c r="AL43" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Yadav (L1 Support)</t>
+        </is>
+      </c>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO43" s="3" t="inlineStr">
+        <is>
+          <t>L64-6</t>
+        </is>
+      </c>
+      <c r="AP43" s="3" t="inlineStr">
+        <is>
+          <t>85.34991</t>
+        </is>
+      </c>
+      <c r="AQ43" s="3" t="inlineStr"/>
+      <c r="AR43" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv setbox issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>2h 55m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv setbox issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX43" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 3:48 PM</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334285</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>Suman Darlami Magar</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>Suman Darlami Magar</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>9861757307</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:53:46 AM</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t>9861757307</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:53:46 AM</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:48:09 PM</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y44" s="3" t="inlineStr">
+        <is>
+          <t>27.70966</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA44" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB44" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC44" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD44" s="3" t="inlineStr"/>
+      <c r="AE44" s="3" t="inlineStr">
+        <is>
+          <t>Sitapaila near Miracle International Model Academy, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF44" s="3" t="inlineStr">
+        <is>
+          <t>magarsuman375@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG44" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH44" s="3" t="inlineStr"/>
+      <c r="AI44" s="3" t="inlineStr">
+        <is>
+          <t>04:54 hour</t>
+        </is>
+      </c>
+      <c r="AJ44" s="3" t="inlineStr"/>
+      <c r="AK44" s="3" t="inlineStr"/>
+      <c r="AL44" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM44" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN44" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO44" s="3" t="inlineStr">
+        <is>
+          <t>1,16</t>
+        </is>
+      </c>
+      <c r="AP44" s="3" t="inlineStr">
+        <is>
+          <t>85.27402</t>
+        </is>
+      </c>
+      <c r="AQ44" s="3" t="inlineStr"/>
+      <c r="AR44" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS44" s="3" t="inlineStr">
+        <is>
+          <t>4h 54m</t>
+        </is>
+      </c>
+      <c r="AT44" s="3" t="inlineStr">
+        <is>
+          <t>4h 54m</t>
+        </is>
+      </c>
+      <c r="AU44" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV44" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW44" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX44" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 3:47 PM</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334285</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>Suman Darlami Magar</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>Suman Darlami Magar</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>9861757307</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr"/>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:53:46 AM</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr"/>
+      <c r="T45" s="3" t="inlineStr"/>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t>9861757307</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:53:46 AM</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:48:09 PM</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
+          <t>27.70966</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA45" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB45" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC45" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD45" s="3" t="inlineStr"/>
+      <c r="AE45" s="3" t="inlineStr">
+        <is>
+          <t>Sitapaila near Miracle International Model Academy, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF45" s="3" t="inlineStr">
+        <is>
+          <t>magarsuman375@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG45" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH45" s="3" t="inlineStr"/>
+      <c r="AI45" s="3" t="inlineStr">
+        <is>
+          <t>04:54 hour</t>
+        </is>
+      </c>
+      <c r="AJ45" s="3" t="inlineStr"/>
+      <c r="AK45" s="3" t="inlineStr"/>
+      <c r="AL45" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM45" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN45" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO45" s="3" t="inlineStr">
+        <is>
+          <t>1,16</t>
+        </is>
+      </c>
+      <c r="AP45" s="3" t="inlineStr">
+        <is>
+          <t>85.27402</t>
+        </is>
+      </c>
+      <c r="AQ45" s="3" t="inlineStr"/>
+      <c r="AR45" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>4h 54m</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>4h 54m</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX45" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 3:07 PM</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wif 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>Wif 6</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334295</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>Amin Karki</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>Amin Karki</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>9860189978</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:01:44 AM</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t>9802238348</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:01:44 AM</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:07:09 PM</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t>27.69723</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA46" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB46" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC46" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD46" s="3" t="inlineStr"/>
+      <c r="AE46" s="3" t="inlineStr">
+        <is>
+          <t>Gyanodaya Secondary School Purano Kalimati, Bafal, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF46" s="3" t="inlineStr">
+        <is>
+          <t>khadkanisha4444@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG46" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH46" s="3" t="inlineStr"/>
+      <c r="AI46" s="3" t="inlineStr"/>
+      <c r="AJ46" s="3" t="inlineStr"/>
+      <c r="AK46" s="3" t="inlineStr"/>
+      <c r="AL46" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM46" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN46" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO46" s="3" t="inlineStr">
+        <is>
+          <t>CDB332</t>
+        </is>
+      </c>
+      <c r="AP46" s="3" t="inlineStr">
+        <is>
+          <t>85.283</t>
+        </is>
+      </c>
+      <c r="AQ46" s="3" t="inlineStr"/>
+      <c r="AR46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wif 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
+        <is>
+          <t>4h 5m</t>
+        </is>
+      </c>
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>4h 5m</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wif 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX46" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 3:00 PM</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334280</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>Gopal Prasad Dhakal</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>Gopal Prasad Dhakal</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>9866115651</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q47" s="3" t="inlineStr"/>
+      <c r="R47" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:50:35 AM</t>
+        </is>
+      </c>
+      <c r="S47" s="3" t="inlineStr"/>
+      <c r="T47" s="3" t="inlineStr"/>
+      <c r="U47" s="3" t="inlineStr">
+        <is>
+          <t>9866115651</t>
+        </is>
+      </c>
+      <c r="V47" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:50:35 AM</t>
+        </is>
+      </c>
+      <c r="W47" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:00:23 PM</t>
+        </is>
+      </c>
+      <c r="X47" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y47" s="3" t="inlineStr">
+        <is>
+          <t>27.699615</t>
+        </is>
+      </c>
+      <c r="Z47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA47" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB47" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC47" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD47" s="3" t="inlineStr"/>
+      <c r="AE47" s="3" t="inlineStr">
+        <is>
+          <t>Gyanodaya Secondary School - School Purano Kalimati Bafal Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF47" s="3" t="inlineStr">
+        <is>
+          <t>9866115651m@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG47" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH47" s="3" t="inlineStr"/>
+      <c r="AI47" s="3" t="inlineStr">
+        <is>
+          <t>04:10 hour</t>
+        </is>
+      </c>
+      <c r="AJ47" s="3" t="inlineStr"/>
+      <c r="AK47" s="3" t="inlineStr"/>
+      <c r="AL47" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM47" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN47" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO47" s="3" t="inlineStr">
+        <is>
+          <t>3,9</t>
+        </is>
+      </c>
+      <c r="AP47" s="3" t="inlineStr">
+        <is>
+          <t>85.284092</t>
+        </is>
+      </c>
+      <c r="AQ47" s="3" t="inlineStr"/>
+      <c r="AR47" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
+        <is>
+          <t>4h 9m</t>
+        </is>
+      </c>
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>4h 9m</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV47" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW47" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX47" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>8</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>90.0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>76.6%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>17.0%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.6%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>70.2%</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX47"/>
+  <dimension ref="A1:AX48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -8817,20 +8817,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M38" s="3" t="inlineStr"/>
       <c r="N38" s="3" t="inlineStr">
         <is>
           <t>Gautam shrestha</t>
         </is>
       </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>9851059167</t>
-        </is>
+      <c r="O38" s="3" t="n">
+        <v>9851059167</v>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
@@ -8865,10 +8859,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y38" s="3" t="inlineStr">
-        <is>
-          <t>27.742284</t>
-        </is>
+      <c r="Y38" s="3" t="n">
+        <v>27.742284</v>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
@@ -8920,25 +8912,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN38" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
           <t>L61-3</t>
         </is>
       </c>
-      <c r="AP38" s="3" t="inlineStr">
-        <is>
-          <t>85.316966</t>
-        </is>
+      <c r="AP38" s="3" t="n">
+        <v>85.31696599999999</v>
       </c>
       <c r="AQ38" s="3" t="inlineStr"/>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>Case : Iptv issue  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
@@ -9039,10 +9027,8 @@
           <t>Sunshine Tradelink</t>
         </is>
       </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>9851015418</t>
-        </is>
+      <c r="O39" s="3" t="n">
+        <v>9851015418</v>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
@@ -9077,10 +9063,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y39" s="3" t="inlineStr">
-        <is>
-          <t>27.718612</t>
-        </is>
+      <c r="Y39" s="3" t="n">
+        <v>27.718612</v>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
@@ -9132,25 +9116,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN39" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="AP39" s="3" t="inlineStr">
-        <is>
-          <t>85.315203</t>
-        </is>
+      <c r="AP39" s="3" t="n">
+        <v>85.315203</v>
       </c>
       <c r="AQ39" s="3" t="inlineStr"/>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
@@ -9251,10 +9231,8 @@
           <t>Ajib Shrestha</t>
         </is>
       </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t>9808961772</t>
-        </is>
+      <c r="O40" s="3" t="n">
+        <v>9808961772</v>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
@@ -9289,10 +9267,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y40" s="3" t="inlineStr">
-        <is>
-          <t>27.70676</t>
-        </is>
+      <c r="Y40" s="3" t="n">
+        <v>27.70676</v>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
@@ -9330,10 +9306,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH40" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH40" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI40" s="3" t="inlineStr">
         <is>
@@ -9352,25 +9326,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN40" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN40" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
           <t>3,6</t>
         </is>
       </c>
-      <c r="AP40" s="3" t="inlineStr">
-        <is>
-          <t>85.29837</t>
-        </is>
+      <c r="AP40" s="3" t="n">
+        <v>85.29837000000001</v>
       </c>
       <c r="AQ40" s="3" t="inlineStr"/>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
@@ -9471,10 +9441,8 @@
           <t>Manisha Tamrakar</t>
         </is>
       </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>9851075215</t>
-        </is>
+      <c r="O41" s="3" t="n">
+        <v>9851075215</v>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
@@ -9509,10 +9477,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y41" s="3" t="inlineStr">
-        <is>
-          <t>27.7126</t>
-        </is>
+      <c r="Y41" s="3" t="n">
+        <v>27.7126</v>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
@@ -9564,25 +9530,21 @@
           <t>Rikesh Shrestha</t>
         </is>
       </c>
-      <c r="AN41" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN41" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
           <t>1,7</t>
         </is>
       </c>
-      <c r="AP41" s="3" t="inlineStr">
-        <is>
-          <t>85.30076</t>
-        </is>
+      <c r="AP41" s="3" t="n">
+        <v>85.30076</v>
       </c>
       <c r="AQ41" s="3" t="inlineStr"/>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
@@ -9683,10 +9645,8 @@
           <t>Ashok Budal</t>
         </is>
       </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>9848400804</t>
-        </is>
+      <c r="O42" s="3" t="n">
+        <v>9848400804</v>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
@@ -9721,10 +9681,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y42" s="3" t="inlineStr">
-        <is>
-          <t>27.687</t>
-        </is>
+      <c r="Y42" s="3" t="n">
+        <v>27.687</v>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
@@ -9780,25 +9738,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN42" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN42" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
           <t>L17-5</t>
         </is>
       </c>
-      <c r="AP42" s="3" t="inlineStr">
-        <is>
-          <t>85.34223</t>
-        </is>
+      <c r="AP42" s="3" t="n">
+        <v>85.34223</v>
       </c>
       <c r="AQ42" s="3" t="inlineStr"/>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
@@ -9899,10 +9853,8 @@
           <t>Pramod Dhungel</t>
         </is>
       </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t>9865072901</t>
-        </is>
+      <c r="O43" s="3" t="n">
+        <v>9865072901</v>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
@@ -9937,10 +9889,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y43" s="3" t="inlineStr">
-        <is>
-          <t>27.6962</t>
-        </is>
+      <c r="Y43" s="3" t="n">
+        <v>27.6962</v>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
@@ -9996,25 +9946,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN43" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN43" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
           <t>L64-6</t>
         </is>
       </c>
-      <c r="AP43" s="3" t="inlineStr">
-        <is>
-          <t>85.34991</t>
-        </is>
+      <c r="AP43" s="3" t="n">
+        <v>85.34990999999999</v>
       </c>
       <c r="AQ43" s="3" t="inlineStr"/>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv setbox issue  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
@@ -10105,20 +10051,14 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M44" s="3" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr">
         <is>
           <t>Suman Darlami Magar</t>
         </is>
       </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t>9861757307</t>
-        </is>
+      <c r="O44" s="3" t="n">
+        <v>9861757307</v>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
@@ -10153,10 +10093,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y44" s="3" t="inlineStr">
-        <is>
-          <t>27.70966</t>
-        </is>
+      <c r="Y44" s="3" t="n">
+        <v>27.70966</v>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
@@ -10212,25 +10150,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN44" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN44" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
           <t>1,16</t>
         </is>
       </c>
-      <c r="AP44" s="3" t="inlineStr">
-        <is>
-          <t>85.27402</t>
-        </is>
+      <c r="AP44" s="3" t="n">
+        <v>85.27401999999999</v>
       </c>
       <c r="AQ44" s="3" t="inlineStr"/>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
@@ -10321,20 +10255,14 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="M45" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M45" s="3" t="inlineStr"/>
       <c r="N45" s="3" t="inlineStr">
         <is>
           <t>Suman Darlami Magar</t>
         </is>
       </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t>9861757307</t>
-        </is>
+      <c r="O45" s="3" t="n">
+        <v>9861757307</v>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
@@ -10369,10 +10297,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y45" s="3" t="inlineStr">
-        <is>
-          <t>27.70966</t>
-        </is>
+      <c r="Y45" s="3" t="n">
+        <v>27.70966</v>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
@@ -10428,25 +10354,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN45" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN45" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
           <t>1,16</t>
         </is>
       </c>
-      <c r="AP45" s="3" t="inlineStr">
-        <is>
-          <t>85.27402</t>
-        </is>
+      <c r="AP45" s="3" t="n">
+        <v>85.27401999999999</v>
       </c>
       <c r="AQ45" s="3" t="inlineStr"/>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">
@@ -10547,10 +10469,8 @@
           <t>Amin Karki</t>
         </is>
       </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t>9860189978</t>
-        </is>
+      <c r="O46" s="3" t="n">
+        <v>9860189978</v>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
@@ -10585,10 +10505,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t>27.69723</t>
-        </is>
+      <c r="Y46" s="3" t="n">
+        <v>27.69723</v>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
@@ -10640,25 +10558,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN46" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN46" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
           <t>CDB332</t>
         </is>
       </c>
-      <c r="AP46" s="3" t="inlineStr">
-        <is>
-          <t>85.283</t>
-        </is>
+      <c r="AP46" s="3" t="n">
+        <v>85.283</v>
       </c>
       <c r="AQ46" s="3" t="inlineStr"/>
       <c r="AR46" s="3" t="inlineStr">
         <is>
-          <t>Case : Wif 6   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS46" s="3" t="inlineStr">
@@ -10759,10 +10673,8 @@
           <t>Gopal Prasad Dhakal</t>
         </is>
       </c>
-      <c r="O47" s="3" t="inlineStr">
-        <is>
-          <t>9866115651</t>
-        </is>
+      <c r="O47" s="3" t="n">
+        <v>9866115651</v>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
@@ -10797,10 +10709,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y47" s="3" t="inlineStr">
-        <is>
-          <t>27.699615</t>
-        </is>
+      <c r="Y47" s="3" t="n">
+        <v>27.699615</v>
       </c>
       <c r="Z47" s="3" t="inlineStr">
         <is>
@@ -10856,53 +10766,265 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN47" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN47" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO47" s="3" t="inlineStr">
         <is>
           <t>3,9</t>
         </is>
       </c>
-      <c r="AP47" s="3" t="inlineStr">
-        <is>
-          <t>85.284092</t>
-        </is>
+      <c r="AP47" s="3" t="n">
+        <v>85.284092</v>
       </c>
       <c r="AQ47" s="3" t="inlineStr"/>
       <c r="AR47" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
+        <is>
+          <t>4h 9m</t>
+        </is>
+      </c>
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>4h 9m</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV47" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS47" s="3" t="inlineStr">
-        <is>
-          <t>4h 9m</t>
-        </is>
-      </c>
-      <c r="AT47" s="3" t="inlineStr">
-        <is>
-          <t>4h 9m</t>
-        </is>
-      </c>
-      <c r="AU47" s="3" t="inlineStr">
+      <c r="AW47" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX47" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 4:19 PM</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wif 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>Wif 6</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334295</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>Amin Karki</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>Amin Karki</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
+          <t>9860189978</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q48" s="3" t="inlineStr"/>
+      <c r="R48" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:01:44 AM</t>
+        </is>
+      </c>
+      <c r="S48" s="3" t="inlineStr"/>
+      <c r="T48" s="3" t="inlineStr"/>
+      <c r="U48" s="3" t="inlineStr">
+        <is>
+          <t>9802238348</t>
+        </is>
+      </c>
+      <c r="V48" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:01:44 AM</t>
+        </is>
+      </c>
+      <c r="W48" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:19:22 PM</t>
+        </is>
+      </c>
+      <c r="X48" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y48" s="3" t="inlineStr">
+        <is>
+          <t>27.69723</t>
+        </is>
+      </c>
+      <c r="Z48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA48" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB48" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC48" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD48" s="3" t="inlineStr"/>
+      <c r="AE48" s="3" t="inlineStr">
+        <is>
+          <t>Gyanodaya Secondary School Purano Kalimati, Bafal, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF48" s="3" t="inlineStr">
+        <is>
+          <t>khadkanisha4444@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG48" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH48" s="3" t="inlineStr"/>
+      <c r="AI48" s="3" t="inlineStr">
+        <is>
+          <t>05:18 hour</t>
+        </is>
+      </c>
+      <c r="AJ48" s="3" t="inlineStr"/>
+      <c r="AK48" s="3" t="inlineStr"/>
+      <c r="AL48" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM48" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN48" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO48" s="3" t="inlineStr">
+        <is>
+          <t>CDB332</t>
+        </is>
+      </c>
+      <c r="AP48" s="3" t="inlineStr">
+        <is>
+          <t>85.283</t>
+        </is>
+      </c>
+      <c r="AQ48" s="3" t="inlineStr"/>
+      <c r="AR48" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wif 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>5h 17m</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>5h 17m</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="AV47" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="AW47" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
-        </is>
-      </c>
-      <c r="AX47" s="3" t="inlineStr">
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wif 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX48" s="3" t="inlineStr">
         <is>
           <t>Ajit Shrestha</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Sep_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>7</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C6" s="3" t="n">
-        <v>7</v>
-      </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>81.8%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>76.6%</t>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>17.3%</t>
         </is>
       </c>
     </row>
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>13.5%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>84.8%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>67.3%</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -823,22 +823,22 @@
         <v>8</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -854,23 +854,23 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Fiber wire breakage suspect</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>0</v>
@@ -879,7 +879,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>1</v>
@@ -888,14 +888,14 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Fiber wire breakage suspect</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
@@ -904,7 +904,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>1</v>
@@ -938,14 +938,14 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Replace SKYCOM to NETTV</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0</v>
@@ -954,7 +954,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>1</v>
@@ -963,7 +963,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>Replace SKYCOM to NETTV</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>1</v>
@@ -988,7 +988,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -1001,10 +1001,10 @@
         <v>0</v>
       </c>
       <c r="E9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -1013,14 +1013,14 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0</v>
@@ -1029,7 +1029,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>1</v>
@@ -1038,14 +1038,14 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Blank TV Display</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>0</v>
@@ -1054,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>1</v>
@@ -1063,7 +1063,7 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Channel buffering,feeze issue</t>
+          <t>SKYCOM-Blank TV Display</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
@@ -1076,38 +1076,63 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B14" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="C13" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="F13" s="4" t="n">
+      <c r="C14" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="G13" s="4" t="n">
-        <v>40</v>
+      <c r="F14" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1121,7 +1146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX48"/>
+  <dimension ref="A1:AX53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -10881,10 +10906,8 @@
           <t>Amin Karki</t>
         </is>
       </c>
-      <c r="O48" s="3" t="inlineStr">
-        <is>
-          <t>9860189978</t>
-        </is>
+      <c r="O48" s="3" t="n">
+        <v>9860189978</v>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
@@ -10919,10 +10942,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y48" s="3" t="inlineStr">
-        <is>
-          <t>27.69723</t>
-        </is>
+      <c r="Y48" s="3" t="n">
+        <v>27.69723</v>
       </c>
       <c r="Z48" s="3" t="inlineStr">
         <is>
@@ -10978,55 +10999,1107 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN48" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN48" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO48" s="3" t="inlineStr">
         <is>
           <t>CDB332</t>
         </is>
       </c>
-      <c r="AP48" s="3" t="inlineStr">
-        <is>
-          <t>85.283</t>
-        </is>
+      <c r="AP48" s="3" t="n">
+        <v>85.283</v>
       </c>
       <c r="AQ48" s="3" t="inlineStr"/>
       <c r="AR48" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>5h 17m</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>5h 17m</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
           <t>Case : Wif 6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS48" s="3" t="inlineStr">
-        <is>
-          <t>5h 17m</t>
-        </is>
-      </c>
-      <c r="AT48" s="3" t="inlineStr">
-        <is>
-          <t>5h 17m</t>
-        </is>
-      </c>
-      <c r="AU48" s="3" t="inlineStr">
+      <c r="AW48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX48" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 4:58 PM</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334762</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>Junkeri ale Shrestha</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>Junkeri ale Shrestha</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>9841034591</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr"/>
+      <c r="R49" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:58:24 PM</t>
+        </is>
+      </c>
+      <c r="S49" s="3" t="inlineStr"/>
+      <c r="T49" s="3" t="inlineStr"/>
+      <c r="U49" s="3" t="inlineStr">
+        <is>
+          <t>9841034591</t>
+        </is>
+      </c>
+      <c r="V49" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:36:15 PM</t>
+        </is>
+      </c>
+      <c r="W49" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:58:24 PM</t>
+        </is>
+      </c>
+      <c r="X49" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y49" s="3" t="inlineStr"/>
+      <c r="Z49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA49" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB49" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC49" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD49" s="3" t="inlineStr"/>
+      <c r="AE49" s="3" t="inlineStr">
+        <is>
+          <t>Tenzing Chowk - Bus stop Budhanilkantha 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF49" s="3" t="inlineStr">
+        <is>
+          <t>junkerialeshrestha@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG49" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH49" s="3" t="inlineStr"/>
+      <c r="AI49" s="3" t="inlineStr">
+        <is>
+          <t>01:22 hour</t>
+        </is>
+      </c>
+      <c r="AJ49" s="3" t="inlineStr"/>
+      <c r="AK49" s="3" t="inlineStr"/>
+      <c r="AL49" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM49" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN49" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO49" s="3" t="inlineStr">
+        <is>
+          <t>4,15</t>
+        </is>
+      </c>
+      <c r="AP49" s="3" t="inlineStr"/>
+      <c r="AQ49" s="3" t="inlineStr"/>
+      <c r="AR49" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS49" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>1h 22m</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW49" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX49" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 5:09 PM</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>slow internet</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334412</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>Kishwor Khanal</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>Kishwor Khanal</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
+          <t>9843123637</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q50" s="3" t="inlineStr"/>
+      <c r="R50" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:22:53 PM</t>
+        </is>
+      </c>
+      <c r="S50" s="3" t="inlineStr"/>
+      <c r="T50" s="3" t="inlineStr"/>
+      <c r="U50" s="3" t="inlineStr">
+        <is>
+          <t>9843123637</t>
+        </is>
+      </c>
+      <c r="V50" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:00:05 PM</t>
+        </is>
+      </c>
+      <c r="W50" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:09:04 PM</t>
+        </is>
+      </c>
+      <c r="X50" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y50" s="3" t="inlineStr">
+        <is>
+          <t>27.705894</t>
+        </is>
+      </c>
+      <c r="Z50" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA50" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB50" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC50" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD50" s="3" t="inlineStr"/>
+      <c r="AE50" s="3" t="inlineStr">
+        <is>
+          <t>Purnima Press Details from Google Maps P844+M85, Sahid Nigurna Marg, Kathmandu 44600, Bagmati, Centr</t>
+        </is>
+      </c>
+      <c r="AF50" s="3" t="inlineStr"/>
+      <c r="AG50" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-No internet connection in STB</t>
+        </is>
+      </c>
+      <c r="AH50" s="3" t="inlineStr"/>
+      <c r="AI50" s="3" t="inlineStr"/>
+      <c r="AJ50" s="3" t="inlineStr"/>
+      <c r="AK50" s="3" t="inlineStr"/>
+      <c r="AL50" s="3" t="inlineStr">
+        <is>
+          <t>Sanish Magar</t>
+        </is>
+      </c>
+      <c r="AM50" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN50" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO50" s="3" t="inlineStr">
+        <is>
+          <t>CDB288</t>
+        </is>
+      </c>
+      <c r="AP50" s="3" t="inlineStr">
+        <is>
+          <t>85.306163</t>
+        </is>
+      </c>
+      <c r="AQ50" s="3" t="inlineStr"/>
+      <c r="AR50" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
+        <is>
+          <t>46m</t>
+        </is>
+      </c>
+      <c r="AT50" s="3" t="inlineStr">
+        <is>
+          <t>5h 8m</t>
+        </is>
+      </c>
+      <c r="AU50" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV50" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW50" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX50" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 5:10 PM</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr"/>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334529</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>Bhim Sen Thakuri</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>Bhim Sen Thakuri</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>9861847418</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q51" s="3" t="inlineStr"/>
+      <c r="R51" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:10:54 PM</t>
+        </is>
+      </c>
+      <c r="S51" s="3" t="inlineStr"/>
+      <c r="T51" s="3" t="inlineStr"/>
+      <c r="U51" s="3" t="inlineStr">
+        <is>
+          <t>9861847418</t>
+        </is>
+      </c>
+      <c r="V51" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:12:21 PM</t>
+        </is>
+      </c>
+      <c r="W51" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:10:54 PM</t>
+        </is>
+      </c>
+      <c r="X51" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y51" s="3" t="inlineStr">
+        <is>
+          <t>27.716731</t>
+        </is>
+      </c>
+      <c r="Z51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA51" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB51" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC51" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD51" s="3" t="inlineStr"/>
+      <c r="AE51" s="3" t="inlineStr">
+        <is>
+          <t>Near Bishwa Shiksha Sadan Secondary School (Montessori Based School), Shankar, Boudhanath Marg, Kath</t>
+        </is>
+      </c>
+      <c r="AF51" s="3" t="inlineStr">
+        <is>
+          <t>thakuribhimsen@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG51" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH51" s="3" t="inlineStr"/>
+      <c r="AI51" s="3" t="inlineStr">
+        <is>
+          <t>03:58 hour</t>
+        </is>
+      </c>
+      <c r="AJ51" s="3" t="inlineStr"/>
+      <c r="AK51" s="3" t="inlineStr"/>
+      <c r="AL51" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM51" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN51" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO51" s="3" t="inlineStr">
+        <is>
+          <t>L5-6</t>
+        </is>
+      </c>
+      <c r="AP51" s="3" t="inlineStr">
+        <is>
+          <t>85.349705</t>
+        </is>
+      </c>
+      <c r="AQ51" s="3" t="inlineStr"/>
+      <c r="AR51" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS51" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>3h 58m</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV51" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX51" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 5:02 PM</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr"/>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334791</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>INDIRA RANABHAT</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>INDIRA RANABHAT</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
+          <t>9866471440</t>
+        </is>
+      </c>
+      <c r="P52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q52" s="3" t="inlineStr"/>
+      <c r="R52" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:02:06 PM</t>
+        </is>
+      </c>
+      <c r="S52" s="3" t="inlineStr"/>
+      <c r="T52" s="3" t="inlineStr"/>
+      <c r="U52" s="3" t="inlineStr">
+        <is>
+          <t>9860365129</t>
+        </is>
+      </c>
+      <c r="V52" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:52:57 PM</t>
+        </is>
+      </c>
+      <c r="W52" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:02:06 PM</t>
+        </is>
+      </c>
+      <c r="X52" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y52" s="3" t="inlineStr">
+        <is>
+          <t>27.665254</t>
+        </is>
+      </c>
+      <c r="Z52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA52" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB52" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC52" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD52" s="3" t="inlineStr"/>
+      <c r="AE52" s="3" t="inlineStr">
+        <is>
+          <t>27.665254, 85.374492, Ranabhat toll, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF52" s="3" t="inlineStr"/>
+      <c r="AG52" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH52" s="3" t="inlineStr"/>
+      <c r="AI52" s="3" t="inlineStr">
+        <is>
+          <t>01:10 hour</t>
+        </is>
+      </c>
+      <c r="AJ52" s="3" t="inlineStr"/>
+      <c r="AK52" s="3" t="inlineStr"/>
+      <c r="AL52" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM52" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN52" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO52" s="3" t="inlineStr">
+        <is>
+          <t>L1-1</t>
+        </is>
+      </c>
+      <c r="AP52" s="3" t="inlineStr">
+        <is>
+          <t>85.374492</t>
+        </is>
+      </c>
+      <c r="AQ52" s="3" t="inlineStr"/>
+      <c r="AR52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS52" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT52" s="3" t="inlineStr">
+        <is>
+          <t>1h 9m</t>
+        </is>
+      </c>
+      <c r="AU52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW52" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX52" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 4:41 PM</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334532</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>Om parkash</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>Om parkash</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
+          <t>9851227421</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q53" s="3" t="inlineStr"/>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:41:39 PM</t>
+        </is>
+      </c>
+      <c r="S53" s="3" t="inlineStr"/>
+      <c r="T53" s="3" t="inlineStr"/>
+      <c r="U53" s="3" t="inlineStr">
+        <is>
+          <t>9851227421</t>
+        </is>
+      </c>
+      <c r="V53" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:12:54 PM</t>
+        </is>
+      </c>
+      <c r="W53" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:07:27 PM</t>
+        </is>
+      </c>
+      <c r="X53" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y53" s="3" t="inlineStr">
+        <is>
+          <t>27.657558</t>
+        </is>
+      </c>
+      <c r="Z53" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA53" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB53" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC53" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD53" s="3" t="inlineStr"/>
+      <c r="AE53" s="3" t="inlineStr">
+        <is>
+          <t>Suryabinayak-3, Balkot Details from Google Maps M98J+72Q, Anantalingeshwar View in Google Maps, Bhak</t>
+        </is>
+      </c>
+      <c r="AF53" s="3" t="inlineStr"/>
+      <c r="AG53" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH53" s="3" t="inlineStr"/>
+      <c r="AI53" s="3" t="inlineStr">
+        <is>
+          <t>03:29 hour</t>
+        </is>
+      </c>
+      <c r="AJ53" s="3" t="inlineStr"/>
+      <c r="AK53" s="3" t="inlineStr"/>
+      <c r="AL53" s="3" t="inlineStr">
+        <is>
+          <t>Govinda Chaulagain</t>
+        </is>
+      </c>
+      <c r="AM53" s="3" t="inlineStr">
+        <is>
+          <t>Rabindra Bohora</t>
+        </is>
+      </c>
+      <c r="AN53" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO53" s="3" t="inlineStr">
+        <is>
+          <t>L36-1</t>
+        </is>
+      </c>
+      <c r="AP53" s="3" t="inlineStr">
+        <is>
+          <t>85.319703</t>
+        </is>
+      </c>
+      <c r="AQ53" s="3" t="inlineStr"/>
+      <c r="AR53" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS53" s="3" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="AT53" s="3" t="inlineStr">
+        <is>
+          <t>3h 54m</t>
+        </is>
+      </c>
+      <c r="AU53" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="AV48" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wif 6   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="AW48" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="AX48" s="3" t="inlineStr">
-        <is>
-          <t>Ajit Shrestha</t>
+      <c r="AV53" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW53" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX53" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Sep_2026.xlsx
@@ -11114,10 +11114,8 @@
           <t>Junkeri ale Shrestha</t>
         </is>
       </c>
-      <c r="O49" s="3" t="inlineStr">
-        <is>
-          <t>9841034591</t>
-        </is>
+      <c r="O49" s="3" t="n">
+        <v>9841034591</v>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
@@ -11207,10 +11205,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN49" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN49" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO49" s="3" t="inlineStr">
         <is>
@@ -11221,7 +11217,7 @@
       <c r="AQ49" s="3" t="inlineStr"/>
       <c r="AR49" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS49" s="3" t="inlineStr">
@@ -11322,10 +11318,8 @@
           <t>Kishwor Khanal</t>
         </is>
       </c>
-      <c r="O50" s="3" t="inlineStr">
-        <is>
-          <t>9843123637</t>
-        </is>
+      <c r="O50" s="3" t="n">
+        <v>9843123637</v>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
@@ -11360,10 +11354,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y50" s="3" t="inlineStr">
-        <is>
-          <t>27.705894</t>
-        </is>
+      <c r="Y50" s="3" t="n">
+        <v>27.705894</v>
       </c>
       <c r="Z50" s="3" t="inlineStr">
         <is>
@@ -11411,25 +11403,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN50" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN50" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO50" s="3" t="inlineStr">
         <is>
           <t>CDB288</t>
         </is>
       </c>
-      <c r="AP50" s="3" t="inlineStr">
-        <is>
-          <t>85.306163</t>
-        </is>
+      <c r="AP50" s="3" t="n">
+        <v>85.306163</v>
       </c>
       <c r="AQ50" s="3" t="inlineStr"/>
       <c r="AR50" s="3" t="inlineStr">
         <is>
-          <t>Case : slow internet  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS50" s="3" t="inlineStr">
@@ -11530,10 +11518,8 @@
           <t>Bhim Sen Thakuri</t>
         </is>
       </c>
-      <c r="O51" s="3" t="inlineStr">
-        <is>
-          <t>9861847418</t>
-        </is>
+      <c r="O51" s="3" t="n">
+        <v>9861847418</v>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
@@ -11568,10 +11554,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y51" s="3" t="inlineStr">
-        <is>
-          <t>27.716731</t>
-        </is>
+      <c r="Y51" s="3" t="n">
+        <v>27.716731</v>
       </c>
       <c r="Z51" s="3" t="inlineStr">
         <is>
@@ -11627,25 +11611,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN51" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN51" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO51" s="3" t="inlineStr">
         <is>
           <t>L5-6</t>
         </is>
       </c>
-      <c r="AP51" s="3" t="inlineStr">
-        <is>
-          <t>85.349705</t>
-        </is>
+      <c r="AP51" s="3" t="n">
+        <v>85.349705</v>
       </c>
       <c r="AQ51" s="3" t="inlineStr"/>
       <c r="AR51" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS51" s="3" t="inlineStr">
@@ -11746,10 +11726,8 @@
           <t>INDIRA RANABHAT</t>
         </is>
       </c>
-      <c r="O52" s="3" t="inlineStr">
-        <is>
-          <t>9866471440</t>
-        </is>
+      <c r="O52" s="3" t="n">
+        <v>9866471440</v>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
@@ -11784,10 +11762,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y52" s="3" t="inlineStr">
-        <is>
-          <t>27.665254</t>
-        </is>
+      <c r="Y52" s="3" t="n">
+        <v>27.665254</v>
       </c>
       <c r="Z52" s="3" t="inlineStr">
         <is>
@@ -11839,25 +11815,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN52" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN52" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO52" s="3" t="inlineStr">
         <is>
           <t>L1-1</t>
         </is>
       </c>
-      <c r="AP52" s="3" t="inlineStr">
-        <is>
-          <t>85.374492</t>
-        </is>
+      <c r="AP52" s="3" t="n">
+        <v>85.374492</v>
       </c>
       <c r="AQ52" s="3" t="inlineStr"/>
       <c r="AR52" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS52" s="3" t="inlineStr">
@@ -11958,10 +11930,8 @@
           <t>Om parkash</t>
         </is>
       </c>
-      <c r="O53" s="3" t="inlineStr">
-        <is>
-          <t>9851227421</t>
-        </is>
+      <c r="O53" s="3" t="n">
+        <v>9851227421</v>
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
@@ -11996,10 +11966,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y53" s="3" t="inlineStr">
-        <is>
-          <t>27.657558</t>
-        </is>
+      <c r="Y53" s="3" t="n">
+        <v>27.657558</v>
       </c>
       <c r="Z53" s="3" t="inlineStr">
         <is>
@@ -12051,25 +12019,21 @@
           <t>Rabindra Bohora</t>
         </is>
       </c>
-      <c r="AN53" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN53" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO53" s="3" t="inlineStr">
         <is>
           <t>L36-1</t>
         </is>
       </c>
-      <c r="AP53" s="3" t="inlineStr">
-        <is>
-          <t>85.319703</t>
-        </is>
+      <c r="AP53" s="3" t="n">
+        <v>85.319703</v>
       </c>
       <c r="AQ53" s="3" t="inlineStr"/>
       <c r="AR53" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS53" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Sep_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>84.6%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>78.2%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>16.4%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>12.7%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>86.8%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>69.1%</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>7</v>
@@ -832,7 +832,7 @@
         <v>5</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
@@ -1123,7 +1123,7 @@
         <v>11</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>9</v>
@@ -1132,7 +1132,7 @@
         <v>11</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1146,7 +1146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX53"/>
+  <dimension ref="A1:AX56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -12067,6 +12067,654 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 5:45 PM</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr"/>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334870</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>Raj KC</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>Raj KC</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
+          <t>9851041494</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q54" s="3" t="inlineStr"/>
+      <c r="R54" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:44:50 PM</t>
+        </is>
+      </c>
+      <c r="S54" s="3" t="inlineStr"/>
+      <c r="T54" s="3" t="inlineStr"/>
+      <c r="U54" s="3" t="inlineStr">
+        <is>
+          <t>9851041494</t>
+        </is>
+      </c>
+      <c r="V54" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:46:23 PM</t>
+        </is>
+      </c>
+      <c r="W54" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:45:07 PM</t>
+        </is>
+      </c>
+      <c r="X54" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y54" s="3" t="inlineStr">
+        <is>
+          <t>27.74613</t>
+        </is>
+      </c>
+      <c r="Z54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA54" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB54" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC54" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD54" s="3" t="inlineStr"/>
+      <c r="AE54" s="3" t="inlineStr">
+        <is>
+          <t>Ram Mandir Heights Details from Google Maps Unnamed Road, P9R5+X58, ??????????? 44600 , Bagmati, Cen</t>
+        </is>
+      </c>
+      <c r="AF54" s="3" t="inlineStr">
+        <is>
+          <t>rajkc6431@gmal.com</t>
+        </is>
+      </c>
+      <c r="AG54" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH54" s="3" t="inlineStr"/>
+      <c r="AI54" s="3" t="inlineStr">
+        <is>
+          <t>00:59 hour</t>
+        </is>
+      </c>
+      <c r="AJ54" s="3" t="inlineStr"/>
+      <c r="AK54" s="3" t="inlineStr"/>
+      <c r="AL54" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM54" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN54" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO54" s="3" t="inlineStr">
+        <is>
+          <t>L27-8</t>
+        </is>
+      </c>
+      <c r="AP54" s="3" t="inlineStr">
+        <is>
+          <t>85.36217</t>
+        </is>
+      </c>
+      <c r="AQ54" s="3" t="inlineStr"/>
+      <c r="AR54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS54" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT54" s="3" t="inlineStr">
+        <is>
+          <t>58m</t>
+        </is>
+      </c>
+      <c r="AU54" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW54" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX54" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 5:44 PM</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr"/>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334870</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>Raj KC</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>Raj KC</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>9851041494</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q55" s="3" t="inlineStr"/>
+      <c r="R55" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:44:50 PM</t>
+        </is>
+      </c>
+      <c r="S55" s="3" t="inlineStr"/>
+      <c r="T55" s="3" t="inlineStr"/>
+      <c r="U55" s="3" t="inlineStr">
+        <is>
+          <t>9851041494</t>
+        </is>
+      </c>
+      <c r="V55" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:46:23 PM</t>
+        </is>
+      </c>
+      <c r="W55" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:45:07 PM</t>
+        </is>
+      </c>
+      <c r="X55" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y55" s="3" t="inlineStr">
+        <is>
+          <t>27.74613</t>
+        </is>
+      </c>
+      <c r="Z55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA55" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB55" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC55" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD55" s="3" t="inlineStr"/>
+      <c r="AE55" s="3" t="inlineStr">
+        <is>
+          <t>Ram Mandir Heights Details from Google Maps Unnamed Road, P9R5+X58, ??????????? 44600 , Bagmati, Cen</t>
+        </is>
+      </c>
+      <c r="AF55" s="3" t="inlineStr">
+        <is>
+          <t>rajkc6431@gmal.com</t>
+        </is>
+      </c>
+      <c r="AG55" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH55" s="3" t="inlineStr"/>
+      <c r="AI55" s="3" t="inlineStr">
+        <is>
+          <t>00:59 hour</t>
+        </is>
+      </c>
+      <c r="AJ55" s="3" t="inlineStr"/>
+      <c r="AK55" s="3" t="inlineStr"/>
+      <c r="AL55" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM55" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN55" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO55" s="3" t="inlineStr">
+        <is>
+          <t>L27-8</t>
+        </is>
+      </c>
+      <c r="AP55" s="3" t="inlineStr">
+        <is>
+          <t>85.36217</t>
+        </is>
+      </c>
+      <c r="AQ55" s="3" t="inlineStr"/>
+      <c r="AR55" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS55" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT55" s="3" t="inlineStr">
+        <is>
+          <t>58m</t>
+        </is>
+      </c>
+      <c r="AU55" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV55" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW55" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX55" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 5:21 PM</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr"/>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6 Router   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334870</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>Raj KC</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
+          <t>Raj KC</t>
+        </is>
+      </c>
+      <c r="O56" s="3" t="inlineStr">
+        <is>
+          <t>9851041494</t>
+        </is>
+      </c>
+      <c r="P56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q56" s="3" t="inlineStr"/>
+      <c r="R56" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:44:50 PM</t>
+        </is>
+      </c>
+      <c r="S56" s="3" t="inlineStr"/>
+      <c r="T56" s="3" t="inlineStr"/>
+      <c r="U56" s="3" t="inlineStr">
+        <is>
+          <t>9851041494</t>
+        </is>
+      </c>
+      <c r="V56" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:46:23 PM</t>
+        </is>
+      </c>
+      <c r="W56" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:45:07 PM</t>
+        </is>
+      </c>
+      <c r="X56" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y56" s="3" t="inlineStr">
+        <is>
+          <t>27.74613</t>
+        </is>
+      </c>
+      <c r="Z56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA56" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB56" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC56" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD56" s="3" t="inlineStr"/>
+      <c r="AE56" s="3" t="inlineStr">
+        <is>
+          <t>Ram Mandir Heights Details from Google Maps Unnamed Road, P9R5+X58, ??????????? 44600 , Bagmati, Cen</t>
+        </is>
+      </c>
+      <c r="AF56" s="3" t="inlineStr">
+        <is>
+          <t>rajkc6431@gmal.com</t>
+        </is>
+      </c>
+      <c r="AG56" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH56" s="3" t="inlineStr"/>
+      <c r="AI56" s="3" t="inlineStr">
+        <is>
+          <t>00:59 hour</t>
+        </is>
+      </c>
+      <c r="AJ56" s="3" t="inlineStr"/>
+      <c r="AK56" s="3" t="inlineStr"/>
+      <c r="AL56" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM56" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN56" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO56" s="3" t="inlineStr">
+        <is>
+          <t>L27-8</t>
+        </is>
+      </c>
+      <c r="AP56" s="3" t="inlineStr">
+        <is>
+          <t>85.36217</t>
+        </is>
+      </c>
+      <c r="AQ56" s="3" t="inlineStr"/>
+      <c r="AR56" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6 Router   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS56" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT56" s="3" t="inlineStr">
+        <is>
+          <t>58m</t>
+        </is>
+      </c>
+      <c r="AU56" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV56" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6 Router   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW56" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX56" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Sep_2026.xlsx
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>78.6%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>17.9%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>67.9%</t>
         </is>
       </c>
     </row>
@@ -826,13 +826,13 @@
         <v>6</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>5</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -1126,13 +1126,13 @@
         <v>7</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F14" s="4" t="n">
         <v>11</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1146,7 +1146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX56"/>
+  <dimension ref="A1:AX57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -12134,10 +12134,8 @@
           <t>Raj KC</t>
         </is>
       </c>
-      <c r="O54" s="3" t="inlineStr">
-        <is>
-          <t>9851041494</t>
-        </is>
+      <c r="O54" s="3" t="n">
+        <v>9851041494</v>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
@@ -12172,10 +12170,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y54" s="3" t="inlineStr">
-        <is>
-          <t>27.74613</t>
-        </is>
+      <c r="Y54" s="3" t="n">
+        <v>27.74613</v>
       </c>
       <c r="Z54" s="3" t="inlineStr">
         <is>
@@ -12231,25 +12227,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN54" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN54" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO54" s="3" t="inlineStr">
         <is>
           <t>L27-8</t>
         </is>
       </c>
-      <c r="AP54" s="3" t="inlineStr">
-        <is>
-          <t>85.36217</t>
-        </is>
+      <c r="AP54" s="3" t="n">
+        <v>85.36217000000001</v>
       </c>
       <c r="AQ54" s="3" t="inlineStr"/>
       <c r="AR54" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS54" s="3" t="inlineStr">
@@ -12350,10 +12342,8 @@
           <t>Raj KC</t>
         </is>
       </c>
-      <c r="O55" s="3" t="inlineStr">
-        <is>
-          <t>9851041494</t>
-        </is>
+      <c r="O55" s="3" t="n">
+        <v>9851041494</v>
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
@@ -12388,10 +12378,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y55" s="3" t="inlineStr">
-        <is>
-          <t>27.74613</t>
-        </is>
+      <c r="Y55" s="3" t="n">
+        <v>27.74613</v>
       </c>
       <c r="Z55" s="3" t="inlineStr">
         <is>
@@ -12447,25 +12435,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN55" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN55" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO55" s="3" t="inlineStr">
         <is>
           <t>L27-8</t>
         </is>
       </c>
-      <c r="AP55" s="3" t="inlineStr">
-        <is>
-          <t>85.36217</t>
-        </is>
+      <c r="AP55" s="3" t="n">
+        <v>85.36217000000001</v>
       </c>
       <c r="AQ55" s="3" t="inlineStr"/>
       <c r="AR55" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS55" s="3" t="inlineStr">
@@ -12566,10 +12550,8 @@
           <t>Raj KC</t>
         </is>
       </c>
-      <c r="O56" s="3" t="inlineStr">
-        <is>
-          <t>9851041494</t>
-        </is>
+      <c r="O56" s="3" t="n">
+        <v>9851041494</v>
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
@@ -12604,10 +12586,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y56" s="3" t="inlineStr">
-        <is>
-          <t>27.74613</t>
-        </is>
+      <c r="Y56" s="3" t="n">
+        <v>27.74613</v>
       </c>
       <c r="Z56" s="3" t="inlineStr">
         <is>
@@ -12663,55 +12643,263 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN56" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN56" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO56" s="3" t="inlineStr">
         <is>
           <t>L27-8</t>
         </is>
       </c>
-      <c r="AP56" s="3" t="inlineStr">
-        <is>
-          <t>85.36217</t>
-        </is>
+      <c r="AP56" s="3" t="n">
+        <v>85.36217000000001</v>
       </c>
       <c r="AQ56" s="3" t="inlineStr"/>
       <c r="AR56" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS56" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT56" s="3" t="inlineStr">
+        <is>
+          <t>58m</t>
+        </is>
+      </c>
+      <c r="AU56" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV56" s="3" t="inlineStr">
+        <is>
           <t>Case :  wifi 6 Router   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS56" s="3" t="inlineStr">
+      <c r="AW56" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX56" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 6:15 PM</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr"/>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334286</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>Yognath dhakal</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
+          <t>Yognath dhakal</t>
+        </is>
+      </c>
+      <c r="O57" s="3" t="inlineStr">
+        <is>
+          <t>9749324717</t>
+        </is>
+      </c>
+      <c r="P57" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q57" s="3" t="inlineStr"/>
+      <c r="R57" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 06:15:02 PM</t>
+        </is>
+      </c>
+      <c r="S57" s="3" t="inlineStr"/>
+      <c r="T57" s="3" t="inlineStr"/>
+      <c r="U57" s="3" t="inlineStr">
+        <is>
+          <t>9749324717</t>
+        </is>
+      </c>
+      <c r="V57" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:56:26 AM</t>
+        </is>
+      </c>
+      <c r="W57" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 06:15:02 PM</t>
+        </is>
+      </c>
+      <c r="X57" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y57" s="3" t="inlineStr">
+        <is>
+          <t>27.7229</t>
+        </is>
+      </c>
+      <c r="Z57" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA57" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB57" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC57" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD57" s="3" t="inlineStr"/>
+      <c r="AE57" s="3" t="inlineStr">
+        <is>
+          <t>Thali gajarkot, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF57" s="3" t="inlineStr"/>
+      <c r="AG57" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH57" s="3" t="inlineStr"/>
+      <c r="AI57" s="3" t="inlineStr">
+        <is>
+          <t>07:19 hour</t>
+        </is>
+      </c>
+      <c r="AJ57" s="3" t="inlineStr"/>
+      <c r="AK57" s="3" t="inlineStr"/>
+      <c r="AL57" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM57" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN57" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO57" s="3" t="inlineStr">
+        <is>
+          <t>L53-6</t>
+        </is>
+      </c>
+      <c r="AP57" s="3" t="inlineStr">
+        <is>
+          <t>85.410785</t>
+        </is>
+      </c>
+      <c r="AQ57" s="3" t="inlineStr"/>
+      <c r="AR57" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS57" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT56" s="3" t="inlineStr">
-        <is>
-          <t>58m</t>
-        </is>
-      </c>
-      <c r="AU56" s="3" t="inlineStr">
+      <c r="AT57" s="3" t="inlineStr">
+        <is>
+          <t>7h 18m</t>
+        </is>
+      </c>
+      <c r="AU57" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV56" s="3" t="inlineStr">
-        <is>
-          <t>Case :  wifi 6 Router   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW56" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
-        </is>
-      </c>
-      <c r="AX56" s="3" t="inlineStr">
-        <is>
-          <t>Sabin Giri</t>
+      <c r="AV57" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW57" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX57" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Sep_2026.xlsx
@@ -12758,10 +12758,8 @@
           <t>Yognath dhakal</t>
         </is>
       </c>
-      <c r="O57" s="3" t="inlineStr">
-        <is>
-          <t>9749324717</t>
-        </is>
+      <c r="O57" s="3" t="n">
+        <v>9749324717</v>
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
@@ -12796,10 +12794,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y57" s="3" t="inlineStr">
-        <is>
-          <t>27.7229</t>
-        </is>
+      <c r="Y57" s="3" t="n">
+        <v>27.7229</v>
       </c>
       <c r="Z57" s="3" t="inlineStr">
         <is>
@@ -12851,25 +12847,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN57" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN57" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO57" s="3" t="inlineStr">
         <is>
           <t>L53-6</t>
         </is>
       </c>
-      <c r="AP57" s="3" t="inlineStr">
-        <is>
-          <t>85.410785</t>
-        </is>
+      <c r="AP57" s="3" t="n">
+        <v>85.410785</v>
       </c>
       <c r="AQ57" s="3" t="inlineStr"/>
       <c r="AR57" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS57" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>91.7%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>79.7%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>20.3%</t>
         </is>
       </c>
     </row>
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.6%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>64.4%</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -863,11 +863,11 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
@@ -879,7 +879,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>1</v>
@@ -888,14 +888,14 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Fiber wire breakage suspect</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
@@ -904,7 +904,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>1</v>
@@ -913,17 +913,17 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on 5Ghz</t>
+          <t>Fiber wire breakage suspect</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
@@ -938,17 +938,17 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>Low Wi-Fi Range on 5Ghz</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -963,14 +963,14 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Replace SKYCOM to NETTV</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
@@ -979,7 +979,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>1</v>
@@ -988,7 +988,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>Replace SKYCOM to NETTV</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -1001,10 +1001,10 @@
         <v>0</v>
       </c>
       <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -1013,7 +1013,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -1026,10 +1026,10 @@
         <v>0</v>
       </c>
       <c r="E10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>1</v>
@@ -1038,14 +1038,14 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>0</v>
@@ -1054,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>1</v>
@@ -1063,14 +1063,14 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Blank TV Display</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1079,7 +1079,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>1</v>
@@ -1088,7 +1088,7 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Channel buffering,feeze issue</t>
+          <t>SKYCOM-Blank TV Display</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
@@ -1101,38 +1101,63 @@
         <v>0</v>
       </c>
       <c r="E13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C14" s="4" t="n">
+      <c r="B15" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D15" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E15" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="F15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="G14" s="4" t="n">
-        <v>47</v>
+      <c r="G15" s="4" t="n">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1146,7 +1171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX57"/>
+  <dimension ref="A1:AX60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -12895,6 +12920,642 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 6:47 PM</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr"/>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>Case : sky com to net tv   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>sky com to net tv</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>TKT1333865</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>Dolma Lama</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
+          <t>Dolma Lama</t>
+        </is>
+      </c>
+      <c r="O58" s="3" t="inlineStr">
+        <is>
+          <t>9818723103</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q58" s="3" t="inlineStr"/>
+      <c r="R58" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 06:47:50 PM</t>
+        </is>
+      </c>
+      <c r="S58" s="3" t="inlineStr"/>
+      <c r="T58" s="3" t="inlineStr"/>
+      <c r="U58" s="3" t="inlineStr">
+        <is>
+          <t>9818723103</t>
+        </is>
+      </c>
+      <c r="V58" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 07:05:43 PM</t>
+        </is>
+      </c>
+      <c r="W58" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 06:47:50 PM</t>
+        </is>
+      </c>
+      <c r="X58" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y58" s="3" t="inlineStr"/>
+      <c r="Z58" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA58" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB58" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC58" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD58" s="3" t="inlineStr"/>
+      <c r="AE58" s="3" t="inlineStr">
+        <is>
+          <t>Near Stupa Butcher Shop, M895+5M5, ?????????? ???, Lalitpur 44700, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF58" s="3" t="inlineStr"/>
+      <c r="AG58" s="3" t="inlineStr">
+        <is>
+          <t>Replace SKYCOM to NETTV</t>
+        </is>
+      </c>
+      <c r="AH58" s="3" t="inlineStr"/>
+      <c r="AI58" s="3" t="inlineStr">
+        <is>
+          <t>09:42 hour</t>
+        </is>
+      </c>
+      <c r="AJ58" s="3" t="inlineStr"/>
+      <c r="AK58" s="3" t="inlineStr"/>
+      <c r="AL58" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM58" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN58" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO58" s="3" t="inlineStr">
+        <is>
+          <t>2,10</t>
+        </is>
+      </c>
+      <c r="AP58" s="3" t="inlineStr"/>
+      <c r="AQ58" s="3" t="inlineStr"/>
+      <c r="AR58" s="3" t="inlineStr">
+        <is>
+          <t>Case : sky com to net tv   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS58" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT58" s="3" t="inlineStr">
+        <is>
+          <t>23h 42m</t>
+        </is>
+      </c>
+      <c r="AU58" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV58" s="3" t="inlineStr">
+        <is>
+          <t>Case : sky com to net tv   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW58" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX58" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 6:43 PM</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr"/>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>Case : ssid auto disconnect  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>ssid auto disconnect</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334260</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="O59" s="3" t="inlineStr">
+        <is>
+          <t>9709029533</t>
+        </is>
+      </c>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q59" s="3" t="inlineStr"/>
+      <c r="R59" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:58:58 PM</t>
+        </is>
+      </c>
+      <c r="S59" s="3" t="inlineStr"/>
+      <c r="T59" s="3" t="inlineStr"/>
+      <c r="U59" s="3" t="inlineStr">
+        <is>
+          <t>KLK9709029533</t>
+        </is>
+      </c>
+      <c r="V59" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:38:16 AM</t>
+        </is>
+      </c>
+      <c r="W59" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 06:43:27 PM</t>
+        </is>
+      </c>
+      <c r="X59" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y59" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z59" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA59" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB59" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC59" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD59" s="3" t="inlineStr"/>
+      <c r="AE59" s="3" t="inlineStr">
+        <is>
+          <t>27.6744679, 85.2724591, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF59" s="3" t="inlineStr">
+        <is>
+          <t>9709029533@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG59" s="3" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="AH59" s="3" t="inlineStr"/>
+      <c r="AI59" s="3" t="inlineStr">
+        <is>
+          <t>08:04 hour</t>
+        </is>
+      </c>
+      <c r="AJ59" s="3" t="inlineStr"/>
+      <c r="AK59" s="3" t="inlineStr"/>
+      <c r="AL59" s="3" t="inlineStr">
+        <is>
+          <t>Sitaram Adhikari</t>
+        </is>
+      </c>
+      <c r="AM59" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN59" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO59" s="3" t="inlineStr">
+        <is>
+          <t>CDB226</t>
+        </is>
+      </c>
+      <c r="AP59" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ59" s="3" t="inlineStr"/>
+      <c r="AR59" s="3" t="inlineStr">
+        <is>
+          <t>Case : ssid auto disconnect  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS59" s="3" t="inlineStr">
+        <is>
+          <t>2h 44m</t>
+        </is>
+      </c>
+      <c r="AT59" s="3" t="inlineStr">
+        <is>
+          <t>8h 5m</t>
+        </is>
+      </c>
+      <c r="AU59" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV59" s="3" t="inlineStr">
+        <is>
+          <t>Case : ssid auto disconnect  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW59" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX59" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 6:42 PM</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr"/>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>Case : ssid auto disconnect  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>ssid auto disconnect</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334260</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="O60" s="3" t="inlineStr">
+        <is>
+          <t>9709029533</t>
+        </is>
+      </c>
+      <c r="P60" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q60" s="3" t="inlineStr"/>
+      <c r="R60" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:58:58 PM</t>
+        </is>
+      </c>
+      <c r="S60" s="3" t="inlineStr"/>
+      <c r="T60" s="3" t="inlineStr"/>
+      <c r="U60" s="3" t="inlineStr">
+        <is>
+          <t>KLK9709029533</t>
+        </is>
+      </c>
+      <c r="V60" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:38:16 AM</t>
+        </is>
+      </c>
+      <c r="W60" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 06:43:27 PM</t>
+        </is>
+      </c>
+      <c r="X60" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y60" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z60" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA60" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB60" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC60" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD60" s="3" t="inlineStr"/>
+      <c r="AE60" s="3" t="inlineStr">
+        <is>
+          <t>27.6744679, 85.2724591, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF60" s="3" t="inlineStr">
+        <is>
+          <t>9709029533@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG60" s="3" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="AH60" s="3" t="inlineStr"/>
+      <c r="AI60" s="3" t="inlineStr">
+        <is>
+          <t>08:04 hour</t>
+        </is>
+      </c>
+      <c r="AJ60" s="3" t="inlineStr"/>
+      <c r="AK60" s="3" t="inlineStr"/>
+      <c r="AL60" s="3" t="inlineStr">
+        <is>
+          <t>Sitaram Adhikari</t>
+        </is>
+      </c>
+      <c r="AM60" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN60" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO60" s="3" t="inlineStr">
+        <is>
+          <t>CDB226</t>
+        </is>
+      </c>
+      <c r="AP60" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ60" s="3" t="inlineStr"/>
+      <c r="AR60" s="3" t="inlineStr">
+        <is>
+          <t>Case : ssid auto disconnect  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS60" s="3" t="inlineStr">
+        <is>
+          <t>2h 44m</t>
+        </is>
+      </c>
+      <c r="AT60" s="3" t="inlineStr">
+        <is>
+          <t>8h 5m</t>
+        </is>
+      </c>
+      <c r="AU60" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV60" s="3" t="inlineStr">
+        <is>
+          <t>Case : ssid auto disconnect  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW60" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX60" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Sep_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>79.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.3%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>86.8%</t>
+          <t>87.2%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>65.0%</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>6</v>
@@ -832,7 +832,7 @@
         <v>5</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
@@ -1145,7 +1145,7 @@
         <v>9</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>7</v>
@@ -1157,7 +1157,7 @@
         <v>11</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1171,7 +1171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX60"/>
+  <dimension ref="A1:AX61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -12987,10 +12987,8 @@
           <t>Dolma Lama</t>
         </is>
       </c>
-      <c r="O58" s="3" t="inlineStr">
-        <is>
-          <t>9818723103</t>
-        </is>
+      <c r="O58" s="3" t="n">
+        <v>9818723103</v>
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
@@ -13076,10 +13074,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN58" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN58" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO58" s="3" t="inlineStr">
         <is>
@@ -13090,7 +13086,7 @@
       <c r="AQ58" s="3" t="inlineStr"/>
       <c r="AR58" s="3" t="inlineStr">
         <is>
-          <t>Case : sky com to net tv   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS58" s="3" t="inlineStr">
@@ -13191,10 +13187,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="O59" s="3" t="inlineStr">
-        <is>
-          <t>9709029533</t>
-        </is>
+      <c r="O59" s="3" t="n">
+        <v>9709029533</v>
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
@@ -13229,10 +13223,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y59" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y59" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z59" s="3" t="inlineStr">
         <is>
@@ -13288,25 +13280,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN59" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN59" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO59" s="3" t="inlineStr">
         <is>
           <t>CDB226</t>
         </is>
       </c>
-      <c r="AP59" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP59" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ59" s="3" t="inlineStr"/>
       <c r="AR59" s="3" t="inlineStr">
         <is>
-          <t>Case : ssid auto disconnect  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS59" s="3" t="inlineStr">
@@ -13407,10 +13395,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="O60" s="3" t="inlineStr">
-        <is>
-          <t>9709029533</t>
-        </is>
+      <c r="O60" s="3" t="n">
+        <v>9709029533</v>
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
@@ -13445,10 +13431,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y60" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y60" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z60" s="3" t="inlineStr">
         <is>
@@ -13504,47 +13488,43 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN60" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN60" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO60" s="3" t="inlineStr">
         <is>
           <t>CDB226</t>
         </is>
       </c>
-      <c r="AP60" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP60" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ60" s="3" t="inlineStr"/>
       <c r="AR60" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS60" s="3" t="inlineStr">
+        <is>
+          <t>2h 44m</t>
+        </is>
+      </c>
+      <c r="AT60" s="3" t="inlineStr">
+        <is>
+          <t>8h 5m</t>
+        </is>
+      </c>
+      <c r="AU60" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV60" s="3" t="inlineStr">
+        <is>
           <t>Case : ssid auto disconnect  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS60" s="3" t="inlineStr">
-        <is>
-          <t>2h 44m</t>
-        </is>
-      </c>
-      <c r="AT60" s="3" t="inlineStr">
-        <is>
-          <t>8h 5m</t>
-        </is>
-      </c>
-      <c r="AU60" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV60" s="3" t="inlineStr">
-        <is>
-          <t>Case : ssid auto disconnect  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW60" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
@@ -13553,6 +13533,218 @@
       <c r="AX60" s="3" t="inlineStr">
         <is>
           <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 6:51 PM</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr"/>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334637</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>Om Khadka</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
+          <t>Om Khadka</t>
+        </is>
+      </c>
+      <c r="O61" s="3" t="inlineStr">
+        <is>
+          <t>9851082021</t>
+        </is>
+      </c>
+      <c r="P61" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q61" s="3" t="inlineStr"/>
+      <c r="R61" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 06:51:48 PM</t>
+        </is>
+      </c>
+      <c r="S61" s="3" t="inlineStr"/>
+      <c r="T61" s="3" t="inlineStr"/>
+      <c r="U61" s="3" t="inlineStr">
+        <is>
+          <t>omkhadka_fttx</t>
+        </is>
+      </c>
+      <c r="V61" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:07:36 PM</t>
+        </is>
+      </c>
+      <c r="W61" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 06:51:48 PM</t>
+        </is>
+      </c>
+      <c r="X61" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y61" s="3" t="inlineStr">
+        <is>
+          <t>27.70292</t>
+        </is>
+      </c>
+      <c r="Z61" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA61" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB61" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC61" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD61" s="3" t="inlineStr"/>
+      <c r="AE61" s="3" t="inlineStr">
+        <is>
+          <t>Battisputali,Hotel Miracle Rastriya Banijaya Bank, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF61" s="3" t="inlineStr"/>
+      <c r="AG61" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH61" s="3" t="inlineStr"/>
+      <c r="AI61" s="3" t="inlineStr">
+        <is>
+          <t>04:44 hour</t>
+        </is>
+      </c>
+      <c r="AJ61" s="3" t="inlineStr"/>
+      <c r="AK61" s="3" t="inlineStr"/>
+      <c r="AL61" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM61" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN61" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO61" s="3" t="inlineStr">
+        <is>
+          <t>L33-6</t>
+        </is>
+      </c>
+      <c r="AP61" s="3" t="inlineStr">
+        <is>
+          <t>85.34114</t>
+        </is>
+      </c>
+      <c r="AQ61" s="3" t="inlineStr"/>
+      <c r="AR61" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS61" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT61" s="3" t="inlineStr">
+        <is>
+          <t>4h 44m</t>
+        </is>
+      </c>
+      <c r="AU61" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV61" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW61" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX61" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_15_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_15_Sep_2026.xlsx
@@ -13603,10 +13603,8 @@
           <t>Om Khadka</t>
         </is>
       </c>
-      <c r="O61" s="3" t="inlineStr">
-        <is>
-          <t>9851082021</t>
-        </is>
+      <c r="O61" s="3" t="n">
+        <v>9851082021</v>
       </c>
       <c r="P61" s="3" t="inlineStr">
         <is>
@@ -13641,10 +13639,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y61" s="3" t="inlineStr">
-        <is>
-          <t>27.70292</t>
-        </is>
+      <c r="Y61" s="3" t="n">
+        <v>27.70292</v>
       </c>
       <c r="Z61" s="3" t="inlineStr">
         <is>
@@ -13696,25 +13692,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN61" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN61" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO61" s="3" t="inlineStr">
         <is>
           <t>L33-6</t>
         </is>
       </c>
-      <c r="AP61" s="3" t="inlineStr">
-        <is>
-          <t>85.34114</t>
-        </is>
+      <c r="AP61" s="3" t="n">
+        <v>85.34114</v>
       </c>
       <c r="AQ61" s="3" t="inlineStr"/>
       <c r="AR61" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS61" s="3" t="inlineStr">
